--- a/uploads/EcoTEA Test.xlsx
+++ b/uploads/EcoTEA Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fanyazhuoting/Documents/AStar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65A95050-8738-4E4B-BA6F-63DE247F2099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADB9B45-FEE1-8447-AF04-2F7B7CAED822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16740" tabRatio="728" xr2:uid="{040DC2EE-8E27-44E1-BFFB-EEC7B065C481}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16740" tabRatio="728" activeTab="2" xr2:uid="{040DC2EE-8E27-44E1-BFFB-EEC7B065C481}"/>
   </bookViews>
   <sheets>
     <sheet name="Power" sheetId="1" r:id="rId1"/>
@@ -3542,7 +3542,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="160">
   <si>
     <t>traceability</t>
   </si>
@@ -4481,6 +4481,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4513,27 +4534,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4580,81 +4580,6 @@
           <cell r="E2">
             <v>22.326907459867794</v>
           </cell>
-          <cell r="F2">
-            <v>30.382403210576012</v>
-          </cell>
-          <cell r="G2">
-            <v>31.628347497639275</v>
-          </cell>
-          <cell r="H2">
-            <v>31.293325163175233</v>
-          </cell>
-          <cell r="I2">
-            <v>30.961851542870168</v>
-          </cell>
-          <cell r="J2">
-            <v>30.633889047074412</v>
-          </cell>
-          <cell r="K2">
-            <v>30.477185741037495</v>
-          </cell>
-          <cell r="L2">
-            <v>30.321284028493494</v>
-          </cell>
-          <cell r="M2">
-            <v>30.166179809004817</v>
-          </cell>
-          <cell r="N2">
-            <v>30.011869003109069</v>
-          </cell>
-          <cell r="O2">
-            <v>29.858347552211761</v>
-          </cell>
-          <cell r="P2">
-            <v>29.701602158095497</v>
-          </cell>
-          <cell r="Q2">
-            <v>29.545679619917045</v>
-          </cell>
-          <cell r="R2">
-            <v>29.390575617983966</v>
-          </cell>
-          <cell r="S2">
-            <v>29.23628585528062</v>
-          </cell>
-          <cell r="T2">
-            <v>29.082806057349124</v>
-          </cell>
-          <cell r="U2">
-            <v>28.926016293664233</v>
-          </cell>
-          <cell r="V2">
-            <v>28.770071807080456</v>
-          </cell>
-          <cell r="W2">
-            <v>28.614968040582326</v>
-          </cell>
-          <cell r="X2">
-            <v>28.460700461721935</v>
-          </cell>
-          <cell r="Y2">
-            <v>28.30726456248647</v>
-          </cell>
-          <cell r="Z2">
-            <v>28.30726456248647</v>
-          </cell>
-          <cell r="AA2">
-            <v>28.30726456248647</v>
-          </cell>
-          <cell r="AB2">
-            <v>28.30726456248647</v>
-          </cell>
-          <cell r="AC2">
-            <v>28.30726456248647</v>
-          </cell>
-          <cell r="AD2">
-            <v>28.30726456248647</v>
-          </cell>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -4662,81 +4587,6 @@
           </cell>
           <cell r="E3">
             <v>6.6403576547675849</v>
-          </cell>
-          <cell r="F3">
-            <v>13.235114603964803</v>
-          </cell>
-          <cell r="G3">
-            <v>10.87281360723744</v>
-          </cell>
-          <cell r="H3">
-            <v>10.751349720053494</v>
-          </cell>
-          <cell r="I3">
-            <v>10.631172435498417</v>
-          </cell>
-          <cell r="J3">
-            <v>10.512268125271964</v>
-          </cell>
-          <cell r="K3">
-            <v>10.455454621431183</v>
-          </cell>
-          <cell r="L3">
-            <v>10.398931738995531</v>
-          </cell>
-          <cell r="M3">
-            <v>10.342697991332511</v>
-          </cell>
-          <cell r="N3">
-            <v>10.286751899414277</v>
-          </cell>
-          <cell r="O3">
-            <v>10.231091991778747</v>
-          </cell>
-          <cell r="P3">
-            <v>10.174263228711354</v>
-          </cell>
-          <cell r="Q3">
-            <v>10.117732795846214</v>
-          </cell>
-          <cell r="R3">
-            <v>10.061499127058974</v>
-          </cell>
-          <cell r="S3">
-            <v>10.005560664446866</v>
-          </cell>
-          <cell r="T3">
-            <v>9.9499158582855394</v>
-          </cell>
-          <cell r="U3">
-            <v>9.8930710088271105</v>
-          </cell>
-          <cell r="V3">
-            <v>9.8365326184667374</v>
-          </cell>
-          <cell r="W3">
-            <v>9.7802990350375207</v>
-          </cell>
-          <cell r="X3">
-            <v>9.7243686152796371</v>
-          </cell>
-          <cell r="Y3">
-            <v>9.6687397247923244</v>
-          </cell>
-          <cell r="Z3">
-            <v>9.6687397247923244</v>
-          </cell>
-          <cell r="AA3">
-            <v>9.6687397247923244</v>
-          </cell>
-          <cell r="AB3">
-            <v>9.6687397247923244</v>
-          </cell>
-          <cell r="AC3">
-            <v>9.6687397247923244</v>
-          </cell>
-          <cell r="AD3">
-            <v>9.6687397247923244</v>
           </cell>
         </row>
         <row r="4">
@@ -4746,81 +4596,6 @@
           <cell r="E4">
             <v>47.222222222222229</v>
           </cell>
-          <cell r="F4">
-            <v>58.032770316699249</v>
-          </cell>
-          <cell r="G4">
-            <v>57.35506048110156</v>
-          </cell>
-          <cell r="H4">
-            <v>56.747528701038171</v>
-          </cell>
-          <cell r="I4">
-            <v>56.146432183368198</v>
-          </cell>
-          <cell r="J4">
-            <v>55.551702762765281</v>
-          </cell>
-          <cell r="K4">
-            <v>55.267535921737405</v>
-          </cell>
-          <cell r="L4">
-            <v>54.984822695801867</v>
-          </cell>
-          <cell r="M4">
-            <v>54.703555649197192</v>
-          </cell>
-          <cell r="N4">
-            <v>54.423727384198557</v>
-          </cell>
-          <cell r="O4">
-            <v>54.145330540923112</v>
-          </cell>
-          <cell r="P4">
-            <v>53.861087377085873</v>
-          </cell>
-          <cell r="Q4">
-            <v>53.578336385803148</v>
-          </cell>
-          <cell r="R4">
-            <v>53.29706973371529</v>
-          </cell>
-          <cell r="S4">
-            <v>53.017279628584888</v>
-          </cell>
-          <cell r="T4">
-            <v>52.738958319080972</v>
-          </cell>
-          <cell r="U4">
-            <v>52.454634695166199</v>
-          </cell>
-          <cell r="V4">
-            <v>52.171843902495965</v>
-          </cell>
-          <cell r="W4">
-            <v>51.890577677347437</v>
-          </cell>
-          <cell r="X4">
-            <v>51.610827800548748</v>
-          </cell>
-          <cell r="Y4">
-            <v>51.332586097238796</v>
-          </cell>
-          <cell r="Z4">
-            <v>51.332586097238796</v>
-          </cell>
-          <cell r="AA4">
-            <v>51.332586097238796</v>
-          </cell>
-          <cell r="AB4">
-            <v>51.332586097238796</v>
-          </cell>
-          <cell r="AC4">
-            <v>51.332586097238796</v>
-          </cell>
-          <cell r="AD4">
-            <v>51.332586097238796</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="B5" t="str">
@@ -4828,81 +4603,6 @@
           </cell>
           <cell r="E5">
             <v>44.155057540884314</v>
-          </cell>
-          <cell r="F5">
-            <v>55.602665051483953</v>
-          </cell>
-          <cell r="G5">
-            <v>60.508782556026652</v>
-          </cell>
-          <cell r="H5">
-            <v>59.867845068255285</v>
-          </cell>
-          <cell r="I5">
-            <v>59.233696691847221</v>
-          </cell>
-          <cell r="J5">
-            <v>58.606265513341334</v>
-          </cell>
-          <cell r="K5">
-            <v>58.306473490646958</v>
-          </cell>
-          <cell r="L5">
-            <v>58.008215011441209</v>
-          </cell>
-          <cell r="M5">
-            <v>57.711482231100312</v>
-          </cell>
-          <cell r="N5">
-            <v>57.416267345128539</v>
-          </cell>
-          <cell r="O5">
-            <v>57.122562588952938</v>
-          </cell>
-          <cell r="P5">
-            <v>56.822690046767562</v>
-          </cell>
-          <cell r="Q5">
-            <v>56.524391725651419</v>
-          </cell>
-          <cell r="R5">
-            <v>56.22765936152021</v>
-          </cell>
-          <cell r="S5">
-            <v>55.932484733673</v>
-          </cell>
-          <cell r="T5">
-            <v>55.638859664564578</v>
-          </cell>
-          <cell r="U5">
-            <v>55.338902238128426</v>
-          </cell>
-          <cell r="V5">
-            <v>55.040561927107966</v>
-          </cell>
-          <cell r="W5">
-            <v>54.743830013391751</v>
-          </cell>
-          <cell r="X5">
-            <v>54.448697825868997</v>
-          </cell>
-          <cell r="Y5">
-            <v>54.155156740176182</v>
-          </cell>
-          <cell r="Z5">
-            <v>54.155156740176182</v>
-          </cell>
-          <cell r="AA5">
-            <v>54.155156740176182</v>
-          </cell>
-          <cell r="AB5">
-            <v>54.155156740176182</v>
-          </cell>
-          <cell r="AC5">
-            <v>54.155156740176182</v>
-          </cell>
-          <cell r="AD5">
-            <v>54.155156740176182</v>
           </cell>
         </row>
         <row r="6">
@@ -4912,81 +4612,6 @@
           <cell r="E6">
             <v>10.63728291332543</v>
           </cell>
-          <cell r="F6">
-            <v>22.253995513053638</v>
-          </cell>
-          <cell r="G6">
-            <v>20.01773193282596</v>
-          </cell>
-          <cell r="H6">
-            <v>19.80569469998251</v>
-          </cell>
-          <cell r="I6">
-            <v>19.59590346525027</v>
-          </cell>
-          <cell r="J6">
-            <v>19.388334437960744</v>
-          </cell>
-          <cell r="K6">
-            <v>19.289156168420465</v>
-          </cell>
-          <cell r="L6">
-            <v>19.190485231223789</v>
-          </cell>
-          <cell r="M6">
-            <v>19.092319031184207</v>
-          </cell>
-          <cell r="N6">
-            <v>18.994654986390529</v>
-          </cell>
-          <cell r="O6">
-            <v>18.897490528138949</v>
-          </cell>
-          <cell r="P6">
-            <v>18.798285620852575</v>
-          </cell>
-          <cell r="Q6">
-            <v>18.699601503012556</v>
-          </cell>
-          <cell r="R6">
-            <v>18.601435440664954</v>
-          </cell>
-          <cell r="S6">
-            <v>18.503784714208081</v>
-          </cell>
-          <cell r="T6">
-            <v>18.406646618317165</v>
-          </cell>
-          <cell r="U6">
-            <v>18.307413629319257</v>
-          </cell>
-          <cell r="V6">
-            <v>18.208715620228862</v>
-          </cell>
-          <cell r="W6">
-            <v>18.110549706889159</v>
-          </cell>
-          <cell r="X6">
-            <v>18.012913020692263</v>
-          </cell>
-          <cell r="Y6">
-            <v>17.91580270849537</v>
-          </cell>
-          <cell r="Z6">
-            <v>17.91580270849537</v>
-          </cell>
-          <cell r="AA6">
-            <v>17.91580270849537</v>
-          </cell>
-          <cell r="AB6">
-            <v>17.91580270849537</v>
-          </cell>
-          <cell r="AC6">
-            <v>17.91580270849537</v>
-          </cell>
-          <cell r="AD6">
-            <v>17.91580270849537</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
@@ -4994,81 +4619,6 @@
           </cell>
           <cell r="E7">
             <v>65.419326319823782</v>
-          </cell>
-          <cell r="F7">
-            <v>90.029453840138444</v>
-          </cell>
-          <cell r="G7">
-            <v>85.979686020339827</v>
-          </cell>
-          <cell r="H7">
-            <v>85.068948741727056</v>
-          </cell>
-          <cell r="I7">
-            <v>84.167858420774238</v>
-          </cell>
-          <cell r="J7">
-            <v>83.276312872367996</v>
-          </cell>
-          <cell r="K7">
-            <v>82.850324728270095</v>
-          </cell>
-          <cell r="L7">
-            <v>82.426515665986102</v>
-          </cell>
-          <cell r="M7">
-            <v>82.004874538732736</v>
-          </cell>
-          <cell r="N7">
-            <v>81.585390256746365</v>
-          </cell>
-          <cell r="O7">
-            <v>81.168051786991583</v>
-          </cell>
-          <cell r="P7">
-            <v>80.741949229080291</v>
-          </cell>
-          <cell r="Q7">
-            <v>80.318083553610592</v>
-          </cell>
-          <cell r="R7">
-            <v>79.896443017768505</v>
-          </cell>
-          <cell r="S7">
-            <v>79.477015940385584</v>
-          </cell>
-          <cell r="T7">
-            <v>79.059790701615213</v>
-          </cell>
-          <cell r="U7">
-            <v>78.633567527804558</v>
-          </cell>
-          <cell r="V7">
-            <v>78.209642186966661</v>
-          </cell>
-          <cell r="W7">
-            <v>77.788002291139762</v>
-          </cell>
-          <cell r="X7">
-            <v>77.368635519147489</v>
-          </cell>
-          <cell r="Y7">
-            <v>76.951529616238773</v>
-          </cell>
-          <cell r="Z7">
-            <v>76.951529616238773</v>
-          </cell>
-          <cell r="AA7">
-            <v>76.951529616238773</v>
-          </cell>
-          <cell r="AB7">
-            <v>76.951529616238773</v>
-          </cell>
-          <cell r="AC7">
-            <v>76.951529616238773</v>
-          </cell>
-          <cell r="AD7">
-            <v>76.951529616238773</v>
           </cell>
         </row>
         <row r="8">
@@ -5078,81 +4628,6 @@
           <cell r="E8">
             <v>13.28071530953517</v>
           </cell>
-          <cell r="F8">
-            <v>26.470229207929606</v>
-          </cell>
-          <cell r="G8">
-            <v>21.745627214474879</v>
-          </cell>
-          <cell r="H8">
-            <v>21.502699440106987</v>
-          </cell>
-          <cell r="I8">
-            <v>21.262344870996834</v>
-          </cell>
-          <cell r="J8">
-            <v>21.024536250543928</v>
-          </cell>
-          <cell r="K8">
-            <v>20.910909242862367</v>
-          </cell>
-          <cell r="L8">
-            <v>20.797863477991061</v>
-          </cell>
-          <cell r="M8">
-            <v>20.685395982665021</v>
-          </cell>
-          <cell r="N8">
-            <v>20.573503798828554</v>
-          </cell>
-          <cell r="O8">
-            <v>20.462183983557495</v>
-          </cell>
-          <cell r="P8">
-            <v>20.348526457422707</v>
-          </cell>
-          <cell r="Q8">
-            <v>20.235465591692428</v>
-          </cell>
-          <cell r="R8">
-            <v>20.122998254117949</v>
-          </cell>
-          <cell r="S8">
-            <v>20.011121328893733</v>
-          </cell>
-          <cell r="T8">
-            <v>19.899831716571079</v>
-          </cell>
-          <cell r="U8">
-            <v>19.786142017654221</v>
-          </cell>
-          <cell r="V8">
-            <v>19.673065236933475</v>
-          </cell>
-          <cell r="W8">
-            <v>19.560598070075041</v>
-          </cell>
-          <cell r="X8">
-            <v>19.448737230559274</v>
-          </cell>
-          <cell r="Y8">
-            <v>19.337479449584649</v>
-          </cell>
-          <cell r="Z8">
-            <v>19.337479449584649</v>
-          </cell>
-          <cell r="AA8">
-            <v>19.337479449584649</v>
-          </cell>
-          <cell r="AB8">
-            <v>19.337479449584649</v>
-          </cell>
-          <cell r="AC8">
-            <v>19.337479449584649</v>
-          </cell>
-          <cell r="AD8">
-            <v>19.337479449584649</v>
-          </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
@@ -5160,81 +4635,6 @@
           </cell>
           <cell r="E9">
             <v>41.060677720850293</v>
-          </cell>
-          <cell r="F9">
-            <v>78.490139044618601</v>
-          </cell>
-          <cell r="G9">
-            <v>65.082570809238916</v>
-          </cell>
-          <cell r="H9">
-            <v>64.393185604809275</v>
-          </cell>
-          <cell r="I9">
-            <v>63.711102692747239</v>
-          </cell>
-          <cell r="J9">
-            <v>63.03624472373717</v>
-          </cell>
-          <cell r="K9">
-            <v>62.713791771936549</v>
-          </cell>
-          <cell r="L9">
-            <v>62.392988282387073</v>
-          </cell>
-          <cell r="M9">
-            <v>62.073825817498985</v>
-          </cell>
-          <cell r="N9">
-            <v>61.756295982843831</v>
-          </cell>
-          <cell r="O9">
-            <v>61.440390426933675</v>
-          </cell>
-          <cell r="P9">
-            <v>61.117850869267713</v>
-          </cell>
-          <cell r="Q9">
-            <v>60.79700452620434</v>
-          </cell>
-          <cell r="R9">
-            <v>60.47784250898674</v>
-          </cell>
-          <cell r="S9">
-            <v>60.160355975520822</v>
-          </cell>
-          <cell r="T9">
-            <v>59.844536130130223</v>
-          </cell>
-          <cell r="U9">
-            <v>59.521905271912068</v>
-          </cell>
-          <cell r="V9">
-            <v>59.201013764976501</v>
-          </cell>
-          <cell r="W9">
-            <v>58.88185223222024</v>
-          </cell>
-          <cell r="X9">
-            <v>58.564411347093355</v>
-          </cell>
-          <cell r="Y9">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="Z9">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AA9">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AB9">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AC9">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AD9">
-            <v>58.248681833326735</v>
           </cell>
         </row>
         <row r="10">
@@ -5244,81 +4644,6 @@
           <cell r="E10">
             <v>2.8621688572247468</v>
           </cell>
-          <cell r="F10">
-            <v>5.9184188137226785</v>
-          </cell>
-          <cell r="G10">
-            <v>5.2034954113767284</v>
-          </cell>
-          <cell r="H10">
-            <v>4.5749321479984388</v>
-          </cell>
-          <cell r="I10">
-            <v>4.0222970338417197</v>
-          </cell>
-          <cell r="J10">
-            <v>3.5364182254659782</v>
-          </cell>
-          <cell r="K10">
-            <v>3.444735810793548</v>
-          </cell>
-          <cell r="L10">
-            <v>3.3554302827403641</v>
-          </cell>
-          <cell r="M10">
-            <v>3.2684400200018286</v>
-          </cell>
-          <cell r="N10">
-            <v>3.1837049988191213</v>
-          </cell>
-          <cell r="O10">
-            <v>3.1011667515624746</v>
-          </cell>
-          <cell r="P10">
-            <v>3.063254681733703</v>
-          </cell>
-          <cell r="Q10">
-            <v>3.025806090703024</v>
-          </cell>
-          <cell r="R10">
-            <v>2.9888153123963561</v>
-          </cell>
-          <cell r="S10">
-            <v>2.9522767500079312</v>
-          </cell>
-          <cell r="T10">
-            <v>2.9161848751534856</v>
-          </cell>
-          <cell r="U10">
-            <v>2.8782123917292162</v>
-          </cell>
-          <cell r="V10">
-            <v>2.8407343589516425</v>
-          </cell>
-          <cell r="W10">
-            <v>2.803744338436442</v>
-          </cell>
-          <cell r="X10">
-            <v>2.767235975635348</v>
-          </cell>
-          <cell r="Y10">
-            <v>2.7312029987444961</v>
-          </cell>
-          <cell r="Z10">
-            <v>2.7312029987444961</v>
-          </cell>
-          <cell r="AA10">
-            <v>2.7312029987444961</v>
-          </cell>
-          <cell r="AB10">
-            <v>2.7312029987444961</v>
-          </cell>
-          <cell r="AC10">
-            <v>2.7312029987444961</v>
-          </cell>
-          <cell r="AD10">
-            <v>2.7312029987444961</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
@@ -5326,81 +4651,6 @@
           </cell>
           <cell r="E11">
             <v>3.005277300085984</v>
-          </cell>
-          <cell r="F11">
-            <v>6.2143397544088126</v>
-          </cell>
-          <cell r="G11">
-            <v>5.4636701819455649</v>
-          </cell>
-          <cell r="H11">
-            <v>4.8036787553983613</v>
-          </cell>
-          <cell r="I11">
-            <v>4.2234118855338059</v>
-          </cell>
-          <cell r="J11">
-            <v>3.7132391367392774</v>
-          </cell>
-          <cell r="K11">
-            <v>3.6169726013332255</v>
-          </cell>
-          <cell r="L11">
-            <v>3.5232017968773826</v>
-          </cell>
-          <cell r="M11">
-            <v>3.4318620210019204</v>
-          </cell>
-          <cell r="N11">
-            <v>3.3428902487600776</v>
-          </cell>
-          <cell r="O11">
-            <v>3.2562250891405986</v>
-          </cell>
-          <cell r="P11">
-            <v>3.2164174158203882</v>
-          </cell>
-          <cell r="Q11">
-            <v>3.1770963952381752</v>
-          </cell>
-          <cell r="R11">
-            <v>3.1382560780161741</v>
-          </cell>
-          <cell r="S11">
-            <v>3.099890587508328</v>
-          </cell>
-          <cell r="T11">
-            <v>3.0619941189111599</v>
-          </cell>
-          <cell r="U11">
-            <v>3.022123011315677</v>
-          </cell>
-          <cell r="V11">
-            <v>2.9827710768992248</v>
-          </cell>
-          <cell r="W11">
-            <v>2.9439315553582643</v>
-          </cell>
-          <cell r="X11">
-            <v>2.9055977744171155</v>
-          </cell>
-          <cell r="Y11">
-            <v>2.8677631486817212</v>
-          </cell>
-          <cell r="Z11">
-            <v>2.8677631486817212</v>
-          </cell>
-          <cell r="AA11">
-            <v>2.8677631486817212</v>
-          </cell>
-          <cell r="AB11">
-            <v>2.8677631486817212</v>
-          </cell>
-          <cell r="AC11">
-            <v>2.8677631486817212</v>
-          </cell>
-          <cell r="AD11">
-            <v>2.8677631486817212</v>
           </cell>
         </row>
         <row r="12">
@@ -5410,81 +4660,6 @@
           <cell r="E12">
             <v>13.32847643827696</v>
           </cell>
-          <cell r="F12">
-            <v>13.370494362532524</v>
-          </cell>
-          <cell r="G12">
-            <v>13.41251228678809</v>
-          </cell>
-          <cell r="H12">
-            <v>13.454530211043654</v>
-          </cell>
-          <cell r="I12">
-            <v>13.49654813529922</v>
-          </cell>
-          <cell r="J12">
-            <v>13.538566059554785</v>
-          </cell>
-          <cell r="K12">
-            <v>13.430101185313674</v>
-          </cell>
-          <cell r="L12">
-            <v>13.321636311072565</v>
-          </cell>
-          <cell r="M12">
-            <v>13.213171436831455</v>
-          </cell>
-          <cell r="N12">
-            <v>13.104706562590346</v>
-          </cell>
-          <cell r="O12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="P12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="Q12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="R12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="S12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="T12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="U12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="V12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="W12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="X12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="Y12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="Z12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="AA12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="AB12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="AC12">
-            <v>12.996241688349237</v>
-          </cell>
-          <cell r="AD12">
-            <v>12.996241688349237</v>
-          </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
@@ -5492,81 +4667,6 @@
           </cell>
           <cell r="E13">
             <v>41.060677720850293</v>
-          </cell>
-          <cell r="F13">
-            <v>78.490139044618601</v>
-          </cell>
-          <cell r="G13">
-            <v>65.082570809238916</v>
-          </cell>
-          <cell r="H13">
-            <v>64.393185604809275</v>
-          </cell>
-          <cell r="I13">
-            <v>63.711102692747239</v>
-          </cell>
-          <cell r="J13">
-            <v>63.03624472373717</v>
-          </cell>
-          <cell r="K13">
-            <v>62.713791771936549</v>
-          </cell>
-          <cell r="L13">
-            <v>62.392988282387073</v>
-          </cell>
-          <cell r="M13">
-            <v>62.073825817498985</v>
-          </cell>
-          <cell r="N13">
-            <v>61.756295982843831</v>
-          </cell>
-          <cell r="O13">
-            <v>61.440390426933675</v>
-          </cell>
-          <cell r="P13">
-            <v>61.117850869267713</v>
-          </cell>
-          <cell r="Q13">
-            <v>60.79700452620434</v>
-          </cell>
-          <cell r="R13">
-            <v>60.47784250898674</v>
-          </cell>
-          <cell r="S13">
-            <v>60.160355975520822</v>
-          </cell>
-          <cell r="T13">
-            <v>59.844536130130223</v>
-          </cell>
-          <cell r="U13">
-            <v>59.521905271912068</v>
-          </cell>
-          <cell r="V13">
-            <v>59.201013764976501</v>
-          </cell>
-          <cell r="W13">
-            <v>58.88185223222024</v>
-          </cell>
-          <cell r="X13">
-            <v>58.564411347093355</v>
-          </cell>
-          <cell r="Y13">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="Z13">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AA13">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AB13">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AC13">
-            <v>58.248681833326735</v>
-          </cell>
-          <cell r="AD13">
-            <v>58.248681833326735</v>
           </cell>
         </row>
         <row r="14">
@@ -5576,81 +4676,6 @@
           <cell r="E14">
             <v>49.06449473986784</v>
           </cell>
-          <cell r="F14">
-            <v>67.522090380103833</v>
-          </cell>
-          <cell r="G14">
-            <v>64.484764515254867</v>
-          </cell>
-          <cell r="H14">
-            <v>63.801711556295288</v>
-          </cell>
-          <cell r="I14">
-            <v>63.125893815580682</v>
-          </cell>
-          <cell r="J14">
-            <v>62.457234654275993</v>
-          </cell>
-          <cell r="K14">
-            <v>62.137743546202572</v>
-          </cell>
-          <cell r="L14">
-            <v>61.819886749489577</v>
-          </cell>
-          <cell r="M14">
-            <v>61.503655904049552</v>
-          </cell>
-          <cell r="N14">
-            <v>61.189042692559774</v>
-          </cell>
-          <cell r="O14">
-            <v>60.876038840243687</v>
-          </cell>
-          <cell r="P14">
-            <v>60.556461921810218</v>
-          </cell>
-          <cell r="Q14">
-            <v>60.238562665207944</v>
-          </cell>
-          <cell r="R14">
-            <v>59.922332263326382</v>
-          </cell>
-          <cell r="S14">
-            <v>59.607761955289192</v>
-          </cell>
-          <cell r="T14">
-            <v>59.29484302621141</v>
-          </cell>
-          <cell r="U14">
-            <v>58.975175645853419</v>
-          </cell>
-          <cell r="V14">
-            <v>58.657231640224992</v>
-          </cell>
-          <cell r="W14">
-            <v>58.341001718354818</v>
-          </cell>
-          <cell r="X14">
-            <v>58.026476639360617</v>
-          </cell>
-          <cell r="Y14">
-            <v>57.713647212179083</v>
-          </cell>
-          <cell r="Z14">
-            <v>57.713647212179083</v>
-          </cell>
-          <cell r="AA14">
-            <v>57.713647212179083</v>
-          </cell>
-          <cell r="AB14">
-            <v>57.713647212179083</v>
-          </cell>
-          <cell r="AC14">
-            <v>57.713647212179083</v>
-          </cell>
-          <cell r="AD14">
-            <v>57.713647212179083</v>
-          </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
@@ -5658,81 +4683,6 @@
           </cell>
           <cell r="E15">
             <v>0.85373489746139286</v>
-          </cell>
-          <cell r="F15">
-            <v>0.85635371616526212</v>
-          </cell>
-          <cell r="G15">
-            <v>0.86028194422106607</v>
-          </cell>
-          <cell r="H15">
-            <v>0.86421017227687003</v>
-          </cell>
-          <cell r="I15">
-            <v>0.86813840033267398</v>
-          </cell>
-          <cell r="J15">
-            <v>0.87206662838847793</v>
-          </cell>
-          <cell r="K15">
-            <v>0.87599485644428188</v>
-          </cell>
-          <cell r="L15">
-            <v>0.87992308450008583</v>
-          </cell>
-          <cell r="M15">
-            <v>0.88516072190782447</v>
-          </cell>
-          <cell r="N15">
-            <v>0.88908894996362842</v>
-          </cell>
-          <cell r="O15">
-            <v>0.89432658737136705</v>
-          </cell>
-          <cell r="P15">
-            <v>0.89825481542717101</v>
-          </cell>
-          <cell r="Q15">
-            <v>0.90349245283490953</v>
-          </cell>
-          <cell r="R15">
-            <v>0.90873009024264806</v>
-          </cell>
-          <cell r="S15">
-            <v>0.9139677276503867</v>
-          </cell>
-          <cell r="T15">
-            <v>0.91920536505812533</v>
-          </cell>
-          <cell r="U15">
-            <v>0.92418112059547708</v>
-          </cell>
-          <cell r="V15">
-            <v>0.9291568761328286</v>
-          </cell>
-          <cell r="W15">
-            <v>0.93413263167018035</v>
-          </cell>
-          <cell r="X15">
-            <v>0.93910838720753187</v>
-          </cell>
-          <cell r="Y15">
-            <v>0.94408414274488361</v>
-          </cell>
-          <cell r="Z15">
-            <v>0.94408414274488361</v>
-          </cell>
-          <cell r="AA15">
-            <v>0.94408414274488361</v>
-          </cell>
-          <cell r="AB15">
-            <v>0.94408414274488361</v>
-          </cell>
-          <cell r="AC15">
-            <v>0.94408414274488361</v>
-          </cell>
-          <cell r="AD15">
-            <v>0.94408414274488361</v>
           </cell>
         </row>
         <row r="16">
@@ -5742,240 +4692,15 @@
           <cell r="E16">
             <v>65.752160650128403</v>
           </cell>
-          <cell r="F16">
-            <v>63.172012573984119</v>
-          </cell>
-          <cell r="G16">
-            <v>60.591864497839836</v>
-          </cell>
-          <cell r="H16">
-            <v>58.01171642169556</v>
-          </cell>
-          <cell r="I16">
-            <v>55.431568345551284</v>
-          </cell>
-          <cell r="J16">
-            <v>52.851420269407001</v>
-          </cell>
-          <cell r="K16">
-            <v>50.532529152382907</v>
-          </cell>
-          <cell r="L16">
-            <v>48.213638035358798</v>
-          </cell>
-          <cell r="M16">
-            <v>46.165144730038747</v>
-          </cell>
-          <cell r="N16">
-            <v>44.387049236422754</v>
-          </cell>
-          <cell r="O16">
-            <v>42.608953742806762</v>
-          </cell>
-          <cell r="P16">
-            <v>40.830858249190769</v>
-          </cell>
-          <cell r="Q16">
-            <v>39.052762755574776</v>
-          </cell>
-          <cell r="R16">
-            <v>37.274667261958776</v>
-          </cell>
-          <cell r="S16">
-            <v>35.496571768342783</v>
-          </cell>
-          <cell r="T16">
-            <v>33.71847627472679</v>
-          </cell>
-          <cell r="U16">
-            <v>33.116447686448097</v>
-          </cell>
-          <cell r="V16">
-            <v>32.514419098169412</v>
-          </cell>
-          <cell r="W16">
-            <v>31.912390509890717</v>
-          </cell>
-          <cell r="X16">
-            <v>31.310361921612031</v>
-          </cell>
-          <cell r="Y16">
-            <v>30.708333333333339</v>
-          </cell>
-          <cell r="Z16">
-            <v>30.708333333333339</v>
-          </cell>
-          <cell r="AA16">
-            <v>30.708333333333339</v>
-          </cell>
-          <cell r="AB16">
-            <v>30.708333333333339</v>
-          </cell>
-          <cell r="AC16">
-            <v>30.708333333333339</v>
-          </cell>
-          <cell r="AD16">
-            <v>30.708333333333339</v>
-          </cell>
         </row>
         <row r="17">
           <cell r="E17">
             <v>72.759</v>
           </cell>
-          <cell r="F17">
-            <v>69.489450000000005</v>
-          </cell>
-          <cell r="G17">
-            <v>66.21990000000001</v>
-          </cell>
-          <cell r="H17">
-            <v>62.95035</v>
-          </cell>
-          <cell r="I17">
-            <v>59.680800000000005</v>
-          </cell>
-          <cell r="J17">
-            <v>56.411250000000003</v>
-          </cell>
-          <cell r="K17">
-            <v>54.615300000000005</v>
-          </cell>
-          <cell r="L17">
-            <v>52.81935</v>
-          </cell>
-          <cell r="M17">
-            <v>51.023400000000002</v>
-          </cell>
-          <cell r="N17">
-            <v>49.227449999999997</v>
-          </cell>
-          <cell r="O17">
-            <v>47.4315</v>
-          </cell>
-          <cell r="P17">
-            <v>46.763775000000003</v>
-          </cell>
-          <cell r="Q17">
-            <v>46.096050000000005</v>
-          </cell>
-          <cell r="R17">
-            <v>45.428325000000001</v>
-          </cell>
-          <cell r="S17">
-            <v>44.760599999999997</v>
-          </cell>
-          <cell r="T17">
-            <v>44.092875000000006</v>
-          </cell>
-          <cell r="U17">
-            <v>43.310025000000003</v>
-          </cell>
-          <cell r="V17">
-            <v>42.527175</v>
-          </cell>
-          <cell r="W17">
-            <v>41.744325000000003</v>
-          </cell>
-          <cell r="X17">
-            <v>40.961475000000007</v>
-          </cell>
-          <cell r="Y17">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="Z17">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AA17">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AB17">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AC17">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AD17">
-            <v>40.178625000000004</v>
-          </cell>
         </row>
         <row r="18">
           <cell r="E18">
             <v>65.621250000000003</v>
-          </cell>
-          <cell r="F18">
-            <v>60.555749999999996</v>
-          </cell>
-          <cell r="G18">
-            <v>55.490250000000003</v>
-          </cell>
-          <cell r="H18">
-            <v>50.424749999999996</v>
-          </cell>
-          <cell r="I18">
-            <v>45.359250000000003</v>
-          </cell>
-          <cell r="J18">
-            <v>40.293750000000003</v>
-          </cell>
-          <cell r="K18">
-            <v>38.451750000000004</v>
-          </cell>
-          <cell r="L18">
-            <v>36.609750000000005</v>
-          </cell>
-          <cell r="M18">
-            <v>34.767749999999999</v>
-          </cell>
-          <cell r="N18">
-            <v>32.925750000000001</v>
-          </cell>
-          <cell r="O18">
-            <v>31.083750000000002</v>
-          </cell>
-          <cell r="P18">
-            <v>29.702250000000003</v>
-          </cell>
-          <cell r="Q18">
-            <v>28.32075</v>
-          </cell>
-          <cell r="R18">
-            <v>26.939249999999998</v>
-          </cell>
-          <cell r="S18">
-            <v>25.557750000000002</v>
-          </cell>
-          <cell r="T18">
-            <v>24.17625</v>
-          </cell>
-          <cell r="U18">
-            <v>23.554575000000003</v>
-          </cell>
-          <cell r="V18">
-            <v>22.9329</v>
-          </cell>
-          <cell r="W18">
-            <v>22.311225</v>
-          </cell>
-          <cell r="X18">
-            <v>21.689550000000004</v>
-          </cell>
-          <cell r="Y18">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="Z18">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AA18">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AB18">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AC18">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AD18">
-            <v>21.067875000000001</v>
           </cell>
         </row>
         <row r="19">
@@ -5983,81 +4708,6 @@
             <v>EEE</v>
           </cell>
           <cell r="E19">
-            <v>94.44</v>
-          </cell>
-          <cell r="F19">
-            <v>94.44</v>
-          </cell>
-          <cell r="G19">
-            <v>94.44</v>
-          </cell>
-          <cell r="H19">
-            <v>94.44</v>
-          </cell>
-          <cell r="I19">
-            <v>94.44</v>
-          </cell>
-          <cell r="J19">
-            <v>94.44</v>
-          </cell>
-          <cell r="K19">
-            <v>94.44</v>
-          </cell>
-          <cell r="L19">
-            <v>94.44</v>
-          </cell>
-          <cell r="M19">
-            <v>94.44</v>
-          </cell>
-          <cell r="N19">
-            <v>94.44</v>
-          </cell>
-          <cell r="O19">
-            <v>94.44</v>
-          </cell>
-          <cell r="P19">
-            <v>94.44</v>
-          </cell>
-          <cell r="Q19">
-            <v>94.44</v>
-          </cell>
-          <cell r="R19">
-            <v>94.44</v>
-          </cell>
-          <cell r="S19">
-            <v>94.44</v>
-          </cell>
-          <cell r="T19">
-            <v>94.44</v>
-          </cell>
-          <cell r="U19">
-            <v>94.44</v>
-          </cell>
-          <cell r="V19">
-            <v>94.44</v>
-          </cell>
-          <cell r="W19">
-            <v>94.44</v>
-          </cell>
-          <cell r="X19">
-            <v>94.44</v>
-          </cell>
-          <cell r="Y19">
-            <v>94.44</v>
-          </cell>
-          <cell r="Z19">
-            <v>94.44</v>
-          </cell>
-          <cell r="AA19">
-            <v>94.44</v>
-          </cell>
-          <cell r="AB19">
-            <v>94.44</v>
-          </cell>
-          <cell r="AC19">
-            <v>94.44</v>
-          </cell>
-          <cell r="AD19">
             <v>94.44</v>
           </cell>
         </row>
@@ -6068,81 +4718,6 @@
           <cell r="E20">
             <v>38.454861111111107</v>
           </cell>
-          <cell r="F20">
-            <v>56.837499999999991</v>
-          </cell>
-          <cell r="G20">
-            <v>57.90069444444444</v>
-          </cell>
-          <cell r="H20">
-            <v>57.253866155841138</v>
-          </cell>
-          <cell r="I20">
-            <v>56.613889376734505</v>
-          </cell>
-          <cell r="J20">
-            <v>55.980691532713116</v>
-          </cell>
-          <cell r="K20">
-            <v>55.678144147552977</v>
-          </cell>
-          <cell r="L20">
-            <v>55.377144400546605</v>
-          </cell>
-          <cell r="M20">
-            <v>55.077684374970957</v>
-          </cell>
-          <cell r="N20">
-            <v>54.779756194599855</v>
-          </cell>
-          <cell r="O20">
-            <v>54.483352023496849</v>
-          </cell>
-          <cell r="P20">
-            <v>54.180723378798042</v>
-          </cell>
-          <cell r="Q20">
-            <v>53.879683423697756</v>
-          </cell>
-          <cell r="R20">
-            <v>53.580223818157123</v>
-          </cell>
-          <cell r="S20">
-            <v>53.282336265919525</v>
-          </cell>
-          <cell r="T20">
-            <v>52.986012514280596</v>
-          </cell>
-          <cell r="U20">
-            <v>52.683298205167269</v>
-          </cell>
-          <cell r="V20">
-            <v>52.382215874237062</v>
-          </cell>
-          <cell r="W20">
-            <v>52.082756723251158</v>
-          </cell>
-          <cell r="X20">
-            <v>51.784912001403342</v>
-          </cell>
-          <cell r="Y20">
-            <v>51.488673005064314</v>
-          </cell>
-          <cell r="Z20">
-            <v>51.488673005064314</v>
-          </cell>
-          <cell r="AA20">
-            <v>51.488673005064314</v>
-          </cell>
-          <cell r="AB20">
-            <v>51.488673005064314</v>
-          </cell>
-          <cell r="AC20">
-            <v>51.488673005064314</v>
-          </cell>
-          <cell r="AD20">
-            <v>51.488673005064314</v>
-          </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
@@ -6151,162 +4726,12 @@
           <cell r="E21">
             <v>41.961503069798319</v>
           </cell>
-          <cell r="F21">
-            <v>48.736842105263158</v>
-          </cell>
-          <cell r="G21">
-            <v>50.735478933617124</v>
-          </cell>
-          <cell r="H21">
-            <v>50.198064875112799</v>
-          </cell>
-          <cell r="I21">
-            <v>49.666343359112226</v>
-          </cell>
-          <cell r="J21">
-            <v>49.140254087527481</v>
-          </cell>
-          <cell r="K21">
-            <v>48.888884101066516</v>
-          </cell>
-          <cell r="L21">
-            <v>48.638799962049099</v>
-          </cell>
-          <cell r="M21">
-            <v>48.389995092905359</v>
-          </cell>
-          <cell r="N21">
-            <v>48.142462949712048</v>
-          </cell>
-          <cell r="O21">
-            <v>47.896197022020452</v>
-          </cell>
-          <cell r="P21">
-            <v>47.644759521476963</v>
-          </cell>
-          <cell r="Q21">
-            <v>47.394641975765182</v>
-          </cell>
-          <cell r="R21">
-            <v>47.145837455605445</v>
-          </cell>
-          <cell r="S21">
-            <v>46.89833906809428</v>
-          </cell>
-          <cell r="T21">
-            <v>46.652139956513437</v>
-          </cell>
-          <cell r="U21">
-            <v>46.400631282118241</v>
-          </cell>
-          <cell r="V21">
-            <v>46.150478528659484</v>
-          </cell>
-          <cell r="W21">
-            <v>45.901674386164281</v>
-          </cell>
-          <cell r="X21">
-            <v>45.654211584068932</v>
-          </cell>
-          <cell r="Y21">
-            <v>45.408082891006401</v>
-          </cell>
-          <cell r="Z21">
-            <v>45.408082891006401</v>
-          </cell>
-          <cell r="AA21">
-            <v>45.408082891006401</v>
-          </cell>
-          <cell r="AB21">
-            <v>45.408082891006401</v>
-          </cell>
-          <cell r="AC21">
-            <v>45.408082891006401</v>
-          </cell>
-          <cell r="AD21">
-            <v>45.408082891006401</v>
-          </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
             <v>2MM</v>
           </cell>
           <cell r="E22">
-            <v>0</v>
-          </cell>
-          <cell r="F22">
-            <v>0</v>
-          </cell>
-          <cell r="G22">
-            <v>0</v>
-          </cell>
-          <cell r="H22">
-            <v>0</v>
-          </cell>
-          <cell r="I22">
-            <v>0</v>
-          </cell>
-          <cell r="J22">
-            <v>0</v>
-          </cell>
-          <cell r="K22">
-            <v>0</v>
-          </cell>
-          <cell r="L22">
-            <v>0</v>
-          </cell>
-          <cell r="M22">
-            <v>0</v>
-          </cell>
-          <cell r="N22">
-            <v>0</v>
-          </cell>
-          <cell r="O22">
-            <v>0</v>
-          </cell>
-          <cell r="P22">
-            <v>0</v>
-          </cell>
-          <cell r="Q22">
-            <v>0</v>
-          </cell>
-          <cell r="R22">
-            <v>0</v>
-          </cell>
-          <cell r="S22">
-            <v>0</v>
-          </cell>
-          <cell r="T22">
-            <v>0</v>
-          </cell>
-          <cell r="U22">
-            <v>0</v>
-          </cell>
-          <cell r="V22">
-            <v>0</v>
-          </cell>
-          <cell r="W22">
-            <v>0</v>
-          </cell>
-          <cell r="X22">
-            <v>0</v>
-          </cell>
-          <cell r="Y22">
-            <v>0</v>
-          </cell>
-          <cell r="Z22">
-            <v>0</v>
-          </cell>
-          <cell r="AA22">
-            <v>0</v>
-          </cell>
-          <cell r="AB22">
-            <v>0</v>
-          </cell>
-          <cell r="AC22">
-            <v>0</v>
-          </cell>
-          <cell r="AD22">
             <v>0</v>
           </cell>
         </row>
@@ -6317,162 +4742,12 @@
           <cell r="E23">
             <v>0</v>
           </cell>
-          <cell r="F23">
-            <v>0</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-          <cell r="I23">
-            <v>0</v>
-          </cell>
-          <cell r="J23">
-            <v>0</v>
-          </cell>
-          <cell r="K23">
-            <v>0</v>
-          </cell>
-          <cell r="L23">
-            <v>0</v>
-          </cell>
-          <cell r="M23">
-            <v>0</v>
-          </cell>
-          <cell r="N23">
-            <v>0</v>
-          </cell>
-          <cell r="O23">
-            <v>0</v>
-          </cell>
-          <cell r="P23">
-            <v>0</v>
-          </cell>
-          <cell r="Q23">
-            <v>0</v>
-          </cell>
-          <cell r="R23">
-            <v>0</v>
-          </cell>
-          <cell r="S23">
-            <v>0</v>
-          </cell>
-          <cell r="T23">
-            <v>0</v>
-          </cell>
-          <cell r="U23">
-            <v>0</v>
-          </cell>
-          <cell r="V23">
-            <v>0</v>
-          </cell>
-          <cell r="W23">
-            <v>0</v>
-          </cell>
-          <cell r="X23">
-            <v>0</v>
-          </cell>
-          <cell r="Y23">
-            <v>0</v>
-          </cell>
-          <cell r="Z23">
-            <v>0</v>
-          </cell>
-          <cell r="AA23">
-            <v>0</v>
-          </cell>
-          <cell r="AB23">
-            <v>0</v>
-          </cell>
-          <cell r="AC23">
-            <v>0</v>
-          </cell>
-          <cell r="AD23">
-            <v>0</v>
-          </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
             <v>CFO</v>
           </cell>
           <cell r="E24">
-            <v>0</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
-          </cell>
-          <cell r="G24">
-            <v>0</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-          <cell r="I24">
-            <v>0</v>
-          </cell>
-          <cell r="J24">
-            <v>0</v>
-          </cell>
-          <cell r="K24">
-            <v>0</v>
-          </cell>
-          <cell r="L24">
-            <v>0</v>
-          </cell>
-          <cell r="M24">
-            <v>0</v>
-          </cell>
-          <cell r="N24">
-            <v>0</v>
-          </cell>
-          <cell r="O24">
-            <v>0</v>
-          </cell>
-          <cell r="P24">
-            <v>0</v>
-          </cell>
-          <cell r="Q24">
-            <v>0</v>
-          </cell>
-          <cell r="R24">
-            <v>0</v>
-          </cell>
-          <cell r="S24">
-            <v>0</v>
-          </cell>
-          <cell r="T24">
-            <v>0</v>
-          </cell>
-          <cell r="U24">
-            <v>0</v>
-          </cell>
-          <cell r="V24">
-            <v>0</v>
-          </cell>
-          <cell r="W24">
-            <v>0</v>
-          </cell>
-          <cell r="X24">
-            <v>0</v>
-          </cell>
-          <cell r="Y24">
-            <v>0</v>
-          </cell>
-          <cell r="Z24">
-            <v>0</v>
-          </cell>
-          <cell r="AA24">
-            <v>0</v>
-          </cell>
-          <cell r="AB24">
-            <v>0</v>
-          </cell>
-          <cell r="AC24">
-            <v>0</v>
-          </cell>
-          <cell r="AD24">
             <v>0</v>
           </cell>
         </row>
@@ -6483,162 +4758,12 @@
           <cell r="E25">
             <v>0</v>
           </cell>
-          <cell r="F25">
-            <v>0</v>
-          </cell>
-          <cell r="G25">
-            <v>0</v>
-          </cell>
-          <cell r="H25">
-            <v>0</v>
-          </cell>
-          <cell r="I25">
-            <v>0</v>
-          </cell>
-          <cell r="J25">
-            <v>0</v>
-          </cell>
-          <cell r="K25">
-            <v>0</v>
-          </cell>
-          <cell r="L25">
-            <v>0</v>
-          </cell>
-          <cell r="M25">
-            <v>0</v>
-          </cell>
-          <cell r="N25">
-            <v>0</v>
-          </cell>
-          <cell r="O25">
-            <v>0</v>
-          </cell>
-          <cell r="P25">
-            <v>0</v>
-          </cell>
-          <cell r="Q25">
-            <v>0</v>
-          </cell>
-          <cell r="R25">
-            <v>0</v>
-          </cell>
-          <cell r="S25">
-            <v>0</v>
-          </cell>
-          <cell r="T25">
-            <v>0</v>
-          </cell>
-          <cell r="U25">
-            <v>0</v>
-          </cell>
-          <cell r="V25">
-            <v>0</v>
-          </cell>
-          <cell r="W25">
-            <v>0</v>
-          </cell>
-          <cell r="X25">
-            <v>0</v>
-          </cell>
-          <cell r="Y25">
-            <v>0</v>
-          </cell>
-          <cell r="Z25">
-            <v>0</v>
-          </cell>
-          <cell r="AA25">
-            <v>0</v>
-          </cell>
-          <cell r="AB25">
-            <v>0</v>
-          </cell>
-          <cell r="AC25">
-            <v>0</v>
-          </cell>
-          <cell r="AD25">
-            <v>0</v>
-          </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
             <v>NCW</v>
           </cell>
           <cell r="E26">
-            <v>0</v>
-          </cell>
-          <cell r="F26">
-            <v>0</v>
-          </cell>
-          <cell r="G26">
-            <v>0</v>
-          </cell>
-          <cell r="H26">
-            <v>0</v>
-          </cell>
-          <cell r="I26">
-            <v>0</v>
-          </cell>
-          <cell r="J26">
-            <v>0</v>
-          </cell>
-          <cell r="K26">
-            <v>0</v>
-          </cell>
-          <cell r="L26">
-            <v>0</v>
-          </cell>
-          <cell r="M26">
-            <v>0</v>
-          </cell>
-          <cell r="N26">
-            <v>0</v>
-          </cell>
-          <cell r="O26">
-            <v>0</v>
-          </cell>
-          <cell r="P26">
-            <v>0</v>
-          </cell>
-          <cell r="Q26">
-            <v>0</v>
-          </cell>
-          <cell r="R26">
-            <v>0</v>
-          </cell>
-          <cell r="S26">
-            <v>0</v>
-          </cell>
-          <cell r="T26">
-            <v>0</v>
-          </cell>
-          <cell r="U26">
-            <v>0</v>
-          </cell>
-          <cell r="V26">
-            <v>0</v>
-          </cell>
-          <cell r="W26">
-            <v>0</v>
-          </cell>
-          <cell r="X26">
-            <v>0</v>
-          </cell>
-          <cell r="Y26">
-            <v>0</v>
-          </cell>
-          <cell r="Z26">
-            <v>0</v>
-          </cell>
-          <cell r="AA26">
-            <v>0</v>
-          </cell>
-          <cell r="AB26">
-            <v>0</v>
-          </cell>
-          <cell r="AC26">
-            <v>0</v>
-          </cell>
-          <cell r="AD26">
             <v>0</v>
           </cell>
         </row>
@@ -6649,162 +4774,12 @@
           <cell r="E27">
             <v>0</v>
           </cell>
-          <cell r="F27">
-            <v>0</v>
-          </cell>
-          <cell r="G27">
-            <v>0</v>
-          </cell>
-          <cell r="H27">
-            <v>0</v>
-          </cell>
-          <cell r="I27">
-            <v>0</v>
-          </cell>
-          <cell r="J27">
-            <v>0</v>
-          </cell>
-          <cell r="K27">
-            <v>0</v>
-          </cell>
-          <cell r="L27">
-            <v>0</v>
-          </cell>
-          <cell r="M27">
-            <v>0</v>
-          </cell>
-          <cell r="N27">
-            <v>0</v>
-          </cell>
-          <cell r="O27">
-            <v>0</v>
-          </cell>
-          <cell r="P27">
-            <v>0</v>
-          </cell>
-          <cell r="Q27">
-            <v>0</v>
-          </cell>
-          <cell r="R27">
-            <v>0</v>
-          </cell>
-          <cell r="S27">
-            <v>0</v>
-          </cell>
-          <cell r="T27">
-            <v>0</v>
-          </cell>
-          <cell r="U27">
-            <v>0</v>
-          </cell>
-          <cell r="V27">
-            <v>0</v>
-          </cell>
-          <cell r="W27">
-            <v>0</v>
-          </cell>
-          <cell r="X27">
-            <v>0</v>
-          </cell>
-          <cell r="Y27">
-            <v>0</v>
-          </cell>
-          <cell r="Z27">
-            <v>0</v>
-          </cell>
-          <cell r="AA27">
-            <v>0</v>
-          </cell>
-          <cell r="AB27">
-            <v>0</v>
-          </cell>
-          <cell r="AC27">
-            <v>0</v>
-          </cell>
-          <cell r="AD27">
-            <v>0</v>
-          </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
             <v>NCM</v>
           </cell>
           <cell r="E28">
-            <v>0</v>
-          </cell>
-          <cell r="F28">
-            <v>0</v>
-          </cell>
-          <cell r="G28">
-            <v>0</v>
-          </cell>
-          <cell r="H28">
-            <v>0</v>
-          </cell>
-          <cell r="I28">
-            <v>0</v>
-          </cell>
-          <cell r="J28">
-            <v>0</v>
-          </cell>
-          <cell r="K28">
-            <v>0</v>
-          </cell>
-          <cell r="L28">
-            <v>0</v>
-          </cell>
-          <cell r="M28">
-            <v>0</v>
-          </cell>
-          <cell r="N28">
-            <v>0</v>
-          </cell>
-          <cell r="O28">
-            <v>0</v>
-          </cell>
-          <cell r="P28">
-            <v>0</v>
-          </cell>
-          <cell r="Q28">
-            <v>0</v>
-          </cell>
-          <cell r="R28">
-            <v>0</v>
-          </cell>
-          <cell r="S28">
-            <v>0</v>
-          </cell>
-          <cell r="T28">
-            <v>0</v>
-          </cell>
-          <cell r="U28">
-            <v>0</v>
-          </cell>
-          <cell r="V28">
-            <v>0</v>
-          </cell>
-          <cell r="W28">
-            <v>0</v>
-          </cell>
-          <cell r="X28">
-            <v>0</v>
-          </cell>
-          <cell r="Y28">
-            <v>0</v>
-          </cell>
-          <cell r="Z28">
-            <v>0</v>
-          </cell>
-          <cell r="AA28">
-            <v>0</v>
-          </cell>
-          <cell r="AB28">
-            <v>0</v>
-          </cell>
-          <cell r="AC28">
-            <v>0</v>
-          </cell>
-          <cell r="AD28">
             <v>0</v>
           </cell>
         </row>
@@ -6815,162 +4790,12 @@
           <cell r="E29">
             <v>0</v>
           </cell>
-          <cell r="F29">
-            <v>0</v>
-          </cell>
-          <cell r="G29">
-            <v>0</v>
-          </cell>
-          <cell r="H29">
-            <v>0</v>
-          </cell>
-          <cell r="I29">
-            <v>0</v>
-          </cell>
-          <cell r="J29">
-            <v>0</v>
-          </cell>
-          <cell r="K29">
-            <v>0</v>
-          </cell>
-          <cell r="L29">
-            <v>0</v>
-          </cell>
-          <cell r="M29">
-            <v>0</v>
-          </cell>
-          <cell r="N29">
-            <v>0</v>
-          </cell>
-          <cell r="O29">
-            <v>0</v>
-          </cell>
-          <cell r="P29">
-            <v>0</v>
-          </cell>
-          <cell r="Q29">
-            <v>0</v>
-          </cell>
-          <cell r="R29">
-            <v>0</v>
-          </cell>
-          <cell r="S29">
-            <v>0</v>
-          </cell>
-          <cell r="T29">
-            <v>0</v>
-          </cell>
-          <cell r="U29">
-            <v>0</v>
-          </cell>
-          <cell r="V29">
-            <v>0</v>
-          </cell>
-          <cell r="W29">
-            <v>0</v>
-          </cell>
-          <cell r="X29">
-            <v>0</v>
-          </cell>
-          <cell r="Y29">
-            <v>0</v>
-          </cell>
-          <cell r="Z29">
-            <v>0</v>
-          </cell>
-          <cell r="AA29">
-            <v>0</v>
-          </cell>
-          <cell r="AB29">
-            <v>0</v>
-          </cell>
-          <cell r="AC29">
-            <v>0</v>
-          </cell>
-          <cell r="AD29">
-            <v>0</v>
-          </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
             <v>NCV</v>
           </cell>
           <cell r="E30">
-            <v>0</v>
-          </cell>
-          <cell r="F30">
-            <v>0</v>
-          </cell>
-          <cell r="G30">
-            <v>0</v>
-          </cell>
-          <cell r="H30">
-            <v>0</v>
-          </cell>
-          <cell r="I30">
-            <v>0</v>
-          </cell>
-          <cell r="J30">
-            <v>0</v>
-          </cell>
-          <cell r="K30">
-            <v>0</v>
-          </cell>
-          <cell r="L30">
-            <v>0</v>
-          </cell>
-          <cell r="M30">
-            <v>0</v>
-          </cell>
-          <cell r="N30">
-            <v>0</v>
-          </cell>
-          <cell r="O30">
-            <v>0</v>
-          </cell>
-          <cell r="P30">
-            <v>0</v>
-          </cell>
-          <cell r="Q30">
-            <v>0</v>
-          </cell>
-          <cell r="R30">
-            <v>0</v>
-          </cell>
-          <cell r="S30">
-            <v>0</v>
-          </cell>
-          <cell r="T30">
-            <v>0</v>
-          </cell>
-          <cell r="U30">
-            <v>0</v>
-          </cell>
-          <cell r="V30">
-            <v>0</v>
-          </cell>
-          <cell r="W30">
-            <v>0</v>
-          </cell>
-          <cell r="X30">
-            <v>0</v>
-          </cell>
-          <cell r="Y30">
-            <v>0</v>
-          </cell>
-          <cell r="Z30">
-            <v>0</v>
-          </cell>
-          <cell r="AA30">
-            <v>0</v>
-          </cell>
-          <cell r="AB30">
-            <v>0</v>
-          </cell>
-          <cell r="AC30">
-            <v>0</v>
-          </cell>
-          <cell r="AD30">
             <v>0</v>
           </cell>
         </row>
@@ -6981,162 +4806,12 @@
           <cell r="E31">
             <v>0</v>
           </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-          <cell r="I31">
-            <v>0</v>
-          </cell>
-          <cell r="J31">
-            <v>0</v>
-          </cell>
-          <cell r="K31">
-            <v>0</v>
-          </cell>
-          <cell r="L31">
-            <v>0</v>
-          </cell>
-          <cell r="M31">
-            <v>0</v>
-          </cell>
-          <cell r="N31">
-            <v>0</v>
-          </cell>
-          <cell r="O31">
-            <v>0</v>
-          </cell>
-          <cell r="P31">
-            <v>0</v>
-          </cell>
-          <cell r="Q31">
-            <v>0</v>
-          </cell>
-          <cell r="R31">
-            <v>0</v>
-          </cell>
-          <cell r="S31">
-            <v>0</v>
-          </cell>
-          <cell r="T31">
-            <v>0</v>
-          </cell>
-          <cell r="U31">
-            <v>0</v>
-          </cell>
-          <cell r="V31">
-            <v>0</v>
-          </cell>
-          <cell r="W31">
-            <v>0</v>
-          </cell>
-          <cell r="X31">
-            <v>0</v>
-          </cell>
-          <cell r="Y31">
-            <v>0</v>
-          </cell>
-          <cell r="Z31">
-            <v>0</v>
-          </cell>
-          <cell r="AA31">
-            <v>0</v>
-          </cell>
-          <cell r="AB31">
-            <v>0</v>
-          </cell>
-          <cell r="AC31">
-            <v>0</v>
-          </cell>
-          <cell r="AD31">
-            <v>0</v>
-          </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
             <v>NCA</v>
           </cell>
           <cell r="E32">
-            <v>0</v>
-          </cell>
-          <cell r="F32">
-            <v>0</v>
-          </cell>
-          <cell r="G32">
-            <v>0</v>
-          </cell>
-          <cell r="H32">
-            <v>0</v>
-          </cell>
-          <cell r="I32">
-            <v>0</v>
-          </cell>
-          <cell r="J32">
-            <v>0</v>
-          </cell>
-          <cell r="K32">
-            <v>0</v>
-          </cell>
-          <cell r="L32">
-            <v>0</v>
-          </cell>
-          <cell r="M32">
-            <v>0</v>
-          </cell>
-          <cell r="N32">
-            <v>0</v>
-          </cell>
-          <cell r="O32">
-            <v>0</v>
-          </cell>
-          <cell r="P32">
-            <v>0</v>
-          </cell>
-          <cell r="Q32">
-            <v>0</v>
-          </cell>
-          <cell r="R32">
-            <v>0</v>
-          </cell>
-          <cell r="S32">
-            <v>0</v>
-          </cell>
-          <cell r="T32">
-            <v>0</v>
-          </cell>
-          <cell r="U32">
-            <v>0</v>
-          </cell>
-          <cell r="V32">
-            <v>0</v>
-          </cell>
-          <cell r="W32">
-            <v>0</v>
-          </cell>
-          <cell r="X32">
-            <v>0</v>
-          </cell>
-          <cell r="Y32">
-            <v>0</v>
-          </cell>
-          <cell r="Z32">
-            <v>0</v>
-          </cell>
-          <cell r="AA32">
-            <v>0</v>
-          </cell>
-          <cell r="AB32">
-            <v>0</v>
-          </cell>
-          <cell r="AC32">
-            <v>0</v>
-          </cell>
-          <cell r="AD32">
             <v>0</v>
           </cell>
         </row>
@@ -7147,162 +4822,12 @@
           <cell r="E33">
             <v>0</v>
           </cell>
-          <cell r="F33">
-            <v>0</v>
-          </cell>
-          <cell r="G33">
-            <v>0</v>
-          </cell>
-          <cell r="H33">
-            <v>0</v>
-          </cell>
-          <cell r="I33">
-            <v>0</v>
-          </cell>
-          <cell r="J33">
-            <v>0</v>
-          </cell>
-          <cell r="K33">
-            <v>0</v>
-          </cell>
-          <cell r="L33">
-            <v>0</v>
-          </cell>
-          <cell r="M33">
-            <v>0</v>
-          </cell>
-          <cell r="N33">
-            <v>0</v>
-          </cell>
-          <cell r="O33">
-            <v>0</v>
-          </cell>
-          <cell r="P33">
-            <v>0</v>
-          </cell>
-          <cell r="Q33">
-            <v>0</v>
-          </cell>
-          <cell r="R33">
-            <v>0</v>
-          </cell>
-          <cell r="S33">
-            <v>0</v>
-          </cell>
-          <cell r="T33">
-            <v>0</v>
-          </cell>
-          <cell r="U33">
-            <v>0</v>
-          </cell>
-          <cell r="V33">
-            <v>0</v>
-          </cell>
-          <cell r="W33">
-            <v>0</v>
-          </cell>
-          <cell r="X33">
-            <v>0</v>
-          </cell>
-          <cell r="Y33">
-            <v>0</v>
-          </cell>
-          <cell r="Z33">
-            <v>0</v>
-          </cell>
-          <cell r="AA33">
-            <v>0</v>
-          </cell>
-          <cell r="AB33">
-            <v>0</v>
-          </cell>
-          <cell r="AC33">
-            <v>0</v>
-          </cell>
-          <cell r="AD33">
-            <v>0</v>
-          </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
             <v>AGG</v>
           </cell>
           <cell r="E34">
-            <v>0</v>
-          </cell>
-          <cell r="F34">
-            <v>0</v>
-          </cell>
-          <cell r="G34">
-            <v>0</v>
-          </cell>
-          <cell r="H34">
-            <v>0</v>
-          </cell>
-          <cell r="I34">
-            <v>0</v>
-          </cell>
-          <cell r="J34">
-            <v>0</v>
-          </cell>
-          <cell r="K34">
-            <v>0</v>
-          </cell>
-          <cell r="L34">
-            <v>0</v>
-          </cell>
-          <cell r="M34">
-            <v>0</v>
-          </cell>
-          <cell r="N34">
-            <v>0</v>
-          </cell>
-          <cell r="O34">
-            <v>0</v>
-          </cell>
-          <cell r="P34">
-            <v>0</v>
-          </cell>
-          <cell r="Q34">
-            <v>0</v>
-          </cell>
-          <cell r="R34">
-            <v>0</v>
-          </cell>
-          <cell r="S34">
-            <v>0</v>
-          </cell>
-          <cell r="T34">
-            <v>0</v>
-          </cell>
-          <cell r="U34">
-            <v>0</v>
-          </cell>
-          <cell r="V34">
-            <v>0</v>
-          </cell>
-          <cell r="W34">
-            <v>0</v>
-          </cell>
-          <cell r="X34">
-            <v>0</v>
-          </cell>
-          <cell r="Y34">
-            <v>0</v>
-          </cell>
-          <cell r="Z34">
-            <v>0</v>
-          </cell>
-          <cell r="AA34">
-            <v>0</v>
-          </cell>
-          <cell r="AB34">
-            <v>0</v>
-          </cell>
-          <cell r="AC34">
-            <v>0</v>
-          </cell>
-          <cell r="AD34">
             <v>0</v>
           </cell>
         </row>
@@ -7313,162 +4838,12 @@
           <cell r="E35">
             <v>0</v>
           </cell>
-          <cell r="F35">
-            <v>0</v>
-          </cell>
-          <cell r="G35">
-            <v>0</v>
-          </cell>
-          <cell r="H35">
-            <v>0</v>
-          </cell>
-          <cell r="I35">
-            <v>0</v>
-          </cell>
-          <cell r="J35">
-            <v>0</v>
-          </cell>
-          <cell r="K35">
-            <v>0</v>
-          </cell>
-          <cell r="L35">
-            <v>0</v>
-          </cell>
-          <cell r="M35">
-            <v>0</v>
-          </cell>
-          <cell r="N35">
-            <v>0</v>
-          </cell>
-          <cell r="O35">
-            <v>0</v>
-          </cell>
-          <cell r="P35">
-            <v>0</v>
-          </cell>
-          <cell r="Q35">
-            <v>0</v>
-          </cell>
-          <cell r="R35">
-            <v>0</v>
-          </cell>
-          <cell r="S35">
-            <v>0</v>
-          </cell>
-          <cell r="T35">
-            <v>0</v>
-          </cell>
-          <cell r="U35">
-            <v>0</v>
-          </cell>
-          <cell r="V35">
-            <v>0</v>
-          </cell>
-          <cell r="W35">
-            <v>0</v>
-          </cell>
-          <cell r="X35">
-            <v>0</v>
-          </cell>
-          <cell r="Y35">
-            <v>0</v>
-          </cell>
-          <cell r="Z35">
-            <v>0</v>
-          </cell>
-          <cell r="AA35">
-            <v>0</v>
-          </cell>
-          <cell r="AB35">
-            <v>0</v>
-          </cell>
-          <cell r="AC35">
-            <v>0</v>
-          </cell>
-          <cell r="AD35">
-            <v>0</v>
-          </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
             <v>WSG</v>
           </cell>
           <cell r="E36">
-            <v>0</v>
-          </cell>
-          <cell r="F36">
-            <v>0</v>
-          </cell>
-          <cell r="G36">
-            <v>0</v>
-          </cell>
-          <cell r="H36">
-            <v>0</v>
-          </cell>
-          <cell r="I36">
-            <v>0</v>
-          </cell>
-          <cell r="J36">
-            <v>0</v>
-          </cell>
-          <cell r="K36">
-            <v>0</v>
-          </cell>
-          <cell r="L36">
-            <v>0</v>
-          </cell>
-          <cell r="M36">
-            <v>0</v>
-          </cell>
-          <cell r="N36">
-            <v>0</v>
-          </cell>
-          <cell r="O36">
-            <v>0</v>
-          </cell>
-          <cell r="P36">
-            <v>0</v>
-          </cell>
-          <cell r="Q36">
-            <v>0</v>
-          </cell>
-          <cell r="R36">
-            <v>0</v>
-          </cell>
-          <cell r="S36">
-            <v>0</v>
-          </cell>
-          <cell r="T36">
-            <v>0</v>
-          </cell>
-          <cell r="U36">
-            <v>0</v>
-          </cell>
-          <cell r="V36">
-            <v>0</v>
-          </cell>
-          <cell r="W36">
-            <v>0</v>
-          </cell>
-          <cell r="X36">
-            <v>0</v>
-          </cell>
-          <cell r="Y36">
-            <v>0</v>
-          </cell>
-          <cell r="Z36">
-            <v>0</v>
-          </cell>
-          <cell r="AA36">
-            <v>0</v>
-          </cell>
-          <cell r="AB36">
-            <v>0</v>
-          </cell>
-          <cell r="AC36">
-            <v>0</v>
-          </cell>
-          <cell r="AD36">
             <v>0</v>
           </cell>
         </row>
@@ -7479,162 +4854,12 @@
           <cell r="E37">
             <v>0</v>
           </cell>
-          <cell r="F37">
-            <v>0</v>
-          </cell>
-          <cell r="G37">
-            <v>0</v>
-          </cell>
-          <cell r="H37">
-            <v>0</v>
-          </cell>
-          <cell r="I37">
-            <v>0</v>
-          </cell>
-          <cell r="J37">
-            <v>0</v>
-          </cell>
-          <cell r="K37">
-            <v>0</v>
-          </cell>
-          <cell r="L37">
-            <v>0</v>
-          </cell>
-          <cell r="M37">
-            <v>0</v>
-          </cell>
-          <cell r="N37">
-            <v>0</v>
-          </cell>
-          <cell r="O37">
-            <v>0</v>
-          </cell>
-          <cell r="P37">
-            <v>0</v>
-          </cell>
-          <cell r="Q37">
-            <v>0</v>
-          </cell>
-          <cell r="R37">
-            <v>0</v>
-          </cell>
-          <cell r="S37">
-            <v>0</v>
-          </cell>
-          <cell r="T37">
-            <v>0</v>
-          </cell>
-          <cell r="U37">
-            <v>0</v>
-          </cell>
-          <cell r="V37">
-            <v>0</v>
-          </cell>
-          <cell r="W37">
-            <v>0</v>
-          </cell>
-          <cell r="X37">
-            <v>0</v>
-          </cell>
-          <cell r="Y37">
-            <v>0</v>
-          </cell>
-          <cell r="Z37">
-            <v>0</v>
-          </cell>
-          <cell r="AA37">
-            <v>0</v>
-          </cell>
-          <cell r="AB37">
-            <v>0</v>
-          </cell>
-          <cell r="AC37">
-            <v>0</v>
-          </cell>
-          <cell r="AD37">
-            <v>0</v>
-          </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
             <v>IMP-2</v>
           </cell>
           <cell r="E39">
-            <v>94.44</v>
-          </cell>
-          <cell r="F39">
-            <v>94.44</v>
-          </cell>
-          <cell r="G39">
-            <v>94.44</v>
-          </cell>
-          <cell r="H39">
-            <v>94.44</v>
-          </cell>
-          <cell r="I39">
-            <v>94.44</v>
-          </cell>
-          <cell r="J39">
-            <v>94.44</v>
-          </cell>
-          <cell r="K39">
-            <v>94.44</v>
-          </cell>
-          <cell r="L39">
-            <v>94.44</v>
-          </cell>
-          <cell r="M39">
-            <v>94.44</v>
-          </cell>
-          <cell r="N39">
-            <v>94.44</v>
-          </cell>
-          <cell r="O39">
-            <v>94.44</v>
-          </cell>
-          <cell r="P39">
-            <v>94.44</v>
-          </cell>
-          <cell r="Q39">
-            <v>94.44</v>
-          </cell>
-          <cell r="R39">
-            <v>94.44</v>
-          </cell>
-          <cell r="S39">
-            <v>94.44</v>
-          </cell>
-          <cell r="T39">
-            <v>94.44</v>
-          </cell>
-          <cell r="U39">
-            <v>94.44</v>
-          </cell>
-          <cell r="V39">
-            <v>94.44</v>
-          </cell>
-          <cell r="W39">
-            <v>94.44</v>
-          </cell>
-          <cell r="X39">
-            <v>94.44</v>
-          </cell>
-          <cell r="Y39">
-            <v>94.44</v>
-          </cell>
-          <cell r="Z39">
-            <v>94.44</v>
-          </cell>
-          <cell r="AA39">
-            <v>94.44</v>
-          </cell>
-          <cell r="AB39">
-            <v>94.44</v>
-          </cell>
-          <cell r="AC39">
-            <v>94.44</v>
-          </cell>
-          <cell r="AD39">
             <v>94.44</v>
           </cell>
         </row>
@@ -7645,81 +4870,6 @@
           <cell r="E40">
             <v>72.759</v>
           </cell>
-          <cell r="F40">
-            <v>69.489450000000005</v>
-          </cell>
-          <cell r="G40">
-            <v>66.21990000000001</v>
-          </cell>
-          <cell r="H40">
-            <v>62.95035</v>
-          </cell>
-          <cell r="I40">
-            <v>59.680800000000005</v>
-          </cell>
-          <cell r="J40">
-            <v>56.411250000000003</v>
-          </cell>
-          <cell r="K40">
-            <v>54.615300000000005</v>
-          </cell>
-          <cell r="L40">
-            <v>52.81935</v>
-          </cell>
-          <cell r="M40">
-            <v>51.023400000000002</v>
-          </cell>
-          <cell r="N40">
-            <v>49.227449999999997</v>
-          </cell>
-          <cell r="O40">
-            <v>47.4315</v>
-          </cell>
-          <cell r="P40">
-            <v>46.763775000000003</v>
-          </cell>
-          <cell r="Q40">
-            <v>46.096050000000005</v>
-          </cell>
-          <cell r="R40">
-            <v>45.428325000000001</v>
-          </cell>
-          <cell r="S40">
-            <v>44.760599999999997</v>
-          </cell>
-          <cell r="T40">
-            <v>44.092875000000006</v>
-          </cell>
-          <cell r="U40">
-            <v>43.310025000000003</v>
-          </cell>
-          <cell r="V40">
-            <v>42.527175</v>
-          </cell>
-          <cell r="W40">
-            <v>41.744325000000003</v>
-          </cell>
-          <cell r="X40">
-            <v>40.961475000000007</v>
-          </cell>
-          <cell r="Y40">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="Z40">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AA40">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AB40">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AC40">
-            <v>40.178625000000004</v>
-          </cell>
-          <cell r="AD40">
-            <v>40.178625000000004</v>
-          </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
@@ -7728,162 +4878,12 @@
           <cell r="E41">
             <v>65.621250000000003</v>
           </cell>
-          <cell r="F41">
-            <v>60.555749999999996</v>
-          </cell>
-          <cell r="G41">
-            <v>55.490250000000003</v>
-          </cell>
-          <cell r="H41">
-            <v>50.424749999999996</v>
-          </cell>
-          <cell r="I41">
-            <v>45.359250000000003</v>
-          </cell>
-          <cell r="J41">
-            <v>40.293750000000003</v>
-          </cell>
-          <cell r="K41">
-            <v>38.451750000000004</v>
-          </cell>
-          <cell r="L41">
-            <v>36.609750000000005</v>
-          </cell>
-          <cell r="M41">
-            <v>34.767749999999999</v>
-          </cell>
-          <cell r="N41">
-            <v>32.925750000000001</v>
-          </cell>
-          <cell r="O41">
-            <v>31.083750000000002</v>
-          </cell>
-          <cell r="P41">
-            <v>29.702250000000003</v>
-          </cell>
-          <cell r="Q41">
-            <v>28.32075</v>
-          </cell>
-          <cell r="R41">
-            <v>26.939249999999998</v>
-          </cell>
-          <cell r="S41">
-            <v>25.557750000000002</v>
-          </cell>
-          <cell r="T41">
-            <v>24.17625</v>
-          </cell>
-          <cell r="U41">
-            <v>23.554575000000003</v>
-          </cell>
-          <cell r="V41">
-            <v>22.9329</v>
-          </cell>
-          <cell r="W41">
-            <v>22.311225</v>
-          </cell>
-          <cell r="X41">
-            <v>21.689550000000004</v>
-          </cell>
-          <cell r="Y41">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="Z41">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AA41">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AB41">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AC41">
-            <v>21.067875000000001</v>
-          </cell>
-          <cell r="AD41">
-            <v>21.067875000000001</v>
-          </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
             <v>IMP-3</v>
           </cell>
           <cell r="E42">
-            <v>94.44</v>
-          </cell>
-          <cell r="F42">
-            <v>94.44</v>
-          </cell>
-          <cell r="G42">
-            <v>94.44</v>
-          </cell>
-          <cell r="H42">
-            <v>94.44</v>
-          </cell>
-          <cell r="I42">
-            <v>94.44</v>
-          </cell>
-          <cell r="J42">
-            <v>94.44</v>
-          </cell>
-          <cell r="K42">
-            <v>94.44</v>
-          </cell>
-          <cell r="L42">
-            <v>94.44</v>
-          </cell>
-          <cell r="M42">
-            <v>94.44</v>
-          </cell>
-          <cell r="N42">
-            <v>94.44</v>
-          </cell>
-          <cell r="O42">
-            <v>94.44</v>
-          </cell>
-          <cell r="P42">
-            <v>94.44</v>
-          </cell>
-          <cell r="Q42">
-            <v>94.44</v>
-          </cell>
-          <cell r="R42">
-            <v>94.44</v>
-          </cell>
-          <cell r="S42">
-            <v>94.44</v>
-          </cell>
-          <cell r="T42">
-            <v>94.44</v>
-          </cell>
-          <cell r="U42">
-            <v>94.44</v>
-          </cell>
-          <cell r="V42">
-            <v>94.44</v>
-          </cell>
-          <cell r="W42">
-            <v>94.44</v>
-          </cell>
-          <cell r="X42">
-            <v>94.44</v>
-          </cell>
-          <cell r="Y42">
-            <v>94.44</v>
-          </cell>
-          <cell r="Z42">
-            <v>94.44</v>
-          </cell>
-          <cell r="AA42">
-            <v>94.44</v>
-          </cell>
-          <cell r="AB42">
-            <v>94.44</v>
-          </cell>
-          <cell r="AC42">
-            <v>94.44</v>
-          </cell>
-          <cell r="AD42">
             <v>94.44</v>
           </cell>
         </row>
@@ -7894,160 +4894,10 @@
           <cell r="E43">
             <v>97.22</v>
           </cell>
-          <cell r="F43">
-            <v>97.22</v>
-          </cell>
-          <cell r="G43">
-            <v>97.22</v>
-          </cell>
-          <cell r="H43">
-            <v>97.22</v>
-          </cell>
-          <cell r="I43">
-            <v>97.22</v>
-          </cell>
-          <cell r="J43">
-            <v>97.22</v>
-          </cell>
-          <cell r="K43">
-            <v>97.22</v>
-          </cell>
-          <cell r="L43">
-            <v>97.22</v>
-          </cell>
-          <cell r="M43">
-            <v>97.22</v>
-          </cell>
-          <cell r="N43">
-            <v>97.22</v>
-          </cell>
-          <cell r="O43">
-            <v>97.22</v>
-          </cell>
-          <cell r="P43">
-            <v>97.22</v>
-          </cell>
-          <cell r="Q43">
-            <v>97.22</v>
-          </cell>
-          <cell r="R43">
-            <v>97.22</v>
-          </cell>
-          <cell r="S43">
-            <v>97.22</v>
-          </cell>
-          <cell r="T43">
-            <v>97.22</v>
-          </cell>
-          <cell r="U43">
-            <v>97.22</v>
-          </cell>
-          <cell r="V43">
-            <v>97.22</v>
-          </cell>
-          <cell r="W43">
-            <v>97.22</v>
-          </cell>
-          <cell r="X43">
-            <v>97.22</v>
-          </cell>
-          <cell r="Y43">
-            <v>97.22</v>
-          </cell>
-          <cell r="Z43">
-            <v>97.22</v>
-          </cell>
-          <cell r="AA43">
-            <v>97.22</v>
-          </cell>
-          <cell r="AB43">
-            <v>97.22</v>
-          </cell>
-          <cell r="AC43">
-            <v>97.22</v>
-          </cell>
-          <cell r="AD43">
-            <v>97.22</v>
-          </cell>
         </row>
         <row r="44">
           <cell r="E44">
             <v>2020</v>
-          </cell>
-          <cell r="F44">
-            <v>2022</v>
-          </cell>
-          <cell r="G44">
-            <v>2024</v>
-          </cell>
-          <cell r="H44">
-            <v>2026</v>
-          </cell>
-          <cell r="I44">
-            <v>2028</v>
-          </cell>
-          <cell r="J44">
-            <v>2030</v>
-          </cell>
-          <cell r="K44">
-            <v>2032</v>
-          </cell>
-          <cell r="L44">
-            <v>2034</v>
-          </cell>
-          <cell r="M44">
-            <v>2036</v>
-          </cell>
-          <cell r="N44">
-            <v>2038</v>
-          </cell>
-          <cell r="O44">
-            <v>2040</v>
-          </cell>
-          <cell r="P44">
-            <v>2042</v>
-          </cell>
-          <cell r="Q44">
-            <v>2044</v>
-          </cell>
-          <cell r="R44">
-            <v>2046</v>
-          </cell>
-          <cell r="S44">
-            <v>2048</v>
-          </cell>
-          <cell r="T44">
-            <v>2050</v>
-          </cell>
-          <cell r="U44">
-            <v>2052</v>
-          </cell>
-          <cell r="V44">
-            <v>2054</v>
-          </cell>
-          <cell r="W44">
-            <v>2056</v>
-          </cell>
-          <cell r="X44">
-            <v>2058</v>
-          </cell>
-          <cell r="Y44">
-            <v>2060</v>
-          </cell>
-          <cell r="Z44">
-            <v>2062</v>
-          </cell>
-          <cell r="AA44">
-            <v>2064</v>
-          </cell>
-          <cell r="AB44">
-            <v>2066</v>
-          </cell>
-          <cell r="AC44">
-            <v>2068</v>
-          </cell>
-          <cell r="AD44">
-            <v>2070</v>
           </cell>
         </row>
         <row r="45">
@@ -8057,81 +4907,6 @@
           <cell r="E45">
             <v>26.120124000000001</v>
           </cell>
-          <cell r="F45">
-            <v>37.935844590821866</v>
-          </cell>
-          <cell r="G45">
-            <v>38.59949855578342</v>
-          </cell>
-          <cell r="H45">
-            <v>35.030629628312838</v>
-          </cell>
-          <cell r="I45">
-            <v>35.212508515621579</v>
-          </cell>
-          <cell r="J45">
-            <v>36.979477069322982</v>
-          </cell>
-          <cell r="K45">
-            <v>38.185759923193977</v>
-          </cell>
-          <cell r="L45">
-            <v>39.224111845529052</v>
-          </cell>
-          <cell r="M45">
-            <v>40.511778123831995</v>
-          </cell>
-          <cell r="N45">
-            <v>41.613391711281018</v>
-          </cell>
-          <cell r="O45">
-            <v>42.979506999619559</v>
-          </cell>
-          <cell r="P45">
-            <v>44.148237151035872</v>
-          </cell>
-          <cell r="Q45">
-            <v>45.597581672246804</v>
-          </cell>
-          <cell r="R45">
-            <v>46.837518228300425</v>
-          </cell>
-          <cell r="S45">
-            <v>48.37516353440499</v>
-          </cell>
-          <cell r="T45">
-            <v>49.69064559884395</v>
-          </cell>
-          <cell r="U45">
-            <v>51.321972329032086</v>
-          </cell>
-          <cell r="V45">
-            <v>52.717603463064819</v>
-          </cell>
-          <cell r="W45">
-            <v>54.448320184298673</v>
-          </cell>
-          <cell r="X45">
-            <v>55.928984527337533</v>
-          </cell>
-          <cell r="Y45">
-            <v>57.765147723587368</v>
-          </cell>
-          <cell r="Z45">
-            <v>57.765147723587368</v>
-          </cell>
-          <cell r="AA45">
-            <v>57.765147723587368</v>
-          </cell>
-          <cell r="AB45">
-            <v>57.765147723587368</v>
-          </cell>
-          <cell r="AC45">
-            <v>57.765147723587368</v>
-          </cell>
-          <cell r="AD45">
-            <v>57.765147723587368</v>
-          </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
@@ -8139,81 +4914,6 @@
           </cell>
           <cell r="E46">
             <v>181.561100638417</v>
-          </cell>
-          <cell r="F46">
-            <v>174.37039946572671</v>
-          </cell>
-          <cell r="G46">
-            <v>167.17969829303641</v>
-          </cell>
-          <cell r="H46">
-            <v>159.98899712034611</v>
-          </cell>
-          <cell r="I46">
-            <v>152.79829594765579</v>
-          </cell>
-          <cell r="J46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="K46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="L46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="M46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="N46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="O46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="P46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="Q46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="R46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="S46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="T46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="U46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="V46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="W46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="X46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="Y46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="Z46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="AA46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="AB46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="AC46">
-            <v>145.60759477496555</v>
-          </cell>
-          <cell r="AD46">
-            <v>145.60759477496555</v>
           </cell>
         </row>
       </sheetData>
@@ -8588,55 +5288,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="48" x14ac:dyDescent="0.2">
@@ -8741,9 +5441,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -8828,37 +5528,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -9117,18 +5817,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -10015,6 +6715,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AJ1:AL2"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="V9:W9"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="Z1:AG1"/>
@@ -10023,12 +6729,6 @@
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z4:AG4"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AJ1:AL2"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="V9:W9"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10078,55 +6778,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -10231,9 +6931,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -10318,37 +7018,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -10607,18 +7307,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -11241,12 +7941,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -11255,6 +7949,12 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -11304,55 +8004,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="48" x14ac:dyDescent="0.2">
@@ -11457,9 +8157,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -11544,37 +8244,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -11833,18 +8533,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -13121,12 +9821,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -13135,6 +9829,12 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -13184,55 +9884,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="48" x14ac:dyDescent="0.2">
@@ -13337,9 +10037,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -13424,37 +10124,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -13713,18 +10413,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
+      <c r="U9" s="52"/>
       <c r="V9" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -13939,71 +10639,28 @@
       <c r="AN11"/>
     </row>
     <row r="12" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="27">
-        <v>2022</v>
-      </c>
-      <c r="L12">
-        <v>2018</v>
-      </c>
-      <c r="M12" t="s">
-        <v>109</v>
-      </c>
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12" s="27"/>
+      <c r="L12"/>
+      <c r="M12"/>
       <c r="N12"/>
-      <c r="O12">
-        <v>94.6</v>
-      </c>
-      <c r="P12" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>90</v>
-      </c>
-      <c r="R12" t="s">
-        <v>109</v>
-      </c>
-      <c r="S12" t="s">
-        <v>61</v>
-      </c>
-      <c r="T12" t="s">
-        <v>109</v>
-      </c>
-      <c r="U12" t="s">
-        <v>107</v>
-      </c>
-      <c r="V12" t="e">
-        <f>SUMIFS([1]Data_BY!F$2:F$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
       <c r="W12"/>
       <c r="X12"/>
       <c r="Y12"/>
@@ -14024,71 +10681,28 @@
       <c r="AN12"/>
     </row>
     <row r="13" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="27">
-        <v>2024</v>
-      </c>
-      <c r="L13">
-        <v>2018</v>
-      </c>
-      <c r="M13" t="s">
-        <v>109</v>
-      </c>
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13" s="27"/>
+      <c r="L13"/>
+      <c r="M13"/>
       <c r="N13"/>
-      <c r="O13">
-        <v>94.6</v>
-      </c>
-      <c r="P13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>90</v>
-      </c>
-      <c r="R13" t="s">
-        <v>109</v>
-      </c>
-      <c r="S13" t="s">
-        <v>61</v>
-      </c>
-      <c r="T13" t="s">
-        <v>109</v>
-      </c>
-      <c r="U13" t="s">
-        <v>107</v>
-      </c>
-      <c r="V13" t="e">
-        <f>SUMIFS([1]Data_BY!G$2:G$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
       <c r="W13"/>
       <c r="X13"/>
       <c r="Y13"/>
@@ -14109,71 +10723,28 @@
       <c r="AN13"/>
     </row>
     <row r="14" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I14" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" s="27">
-        <v>2026</v>
-      </c>
-      <c r="L14">
-        <v>2018</v>
-      </c>
-      <c r="M14" t="s">
-        <v>109</v>
-      </c>
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14" s="27"/>
+      <c r="L14"/>
+      <c r="M14"/>
       <c r="N14"/>
-      <c r="O14">
-        <v>94.6</v>
-      </c>
-      <c r="P14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>90</v>
-      </c>
-      <c r="R14" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14" t="s">
-        <v>61</v>
-      </c>
-      <c r="T14" t="s">
-        <v>109</v>
-      </c>
-      <c r="U14" t="s">
-        <v>107</v>
-      </c>
-      <c r="V14" t="e">
-        <f>SUMIFS([1]Data_BY!H$2:H$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
       <c r="Y14"/>
@@ -14194,71 +10765,28 @@
       <c r="AN14"/>
     </row>
     <row r="15" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" t="s">
-        <v>89</v>
-      </c>
-      <c r="K15" s="27">
-        <v>2028</v>
-      </c>
-      <c r="L15">
-        <v>2018</v>
-      </c>
-      <c r="M15" t="s">
-        <v>109</v>
-      </c>
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15" s="27"/>
+      <c r="L15"/>
+      <c r="M15"/>
       <c r="N15"/>
-      <c r="O15">
-        <v>94.6</v>
-      </c>
-      <c r="P15" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>90</v>
-      </c>
-      <c r="R15" t="s">
-        <v>109</v>
-      </c>
-      <c r="S15" t="s">
-        <v>61</v>
-      </c>
-      <c r="T15" t="s">
-        <v>109</v>
-      </c>
-      <c r="U15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V15" t="e">
-        <f>SUMIFS([1]Data_BY!I$2:I$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
       <c r="W15"/>
       <c r="X15"/>
       <c r="Y15"/>
@@ -14279,71 +10807,28 @@
       <c r="AN15"/>
     </row>
     <row r="16" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" t="s">
-        <v>115</v>
-      </c>
-      <c r="J16" t="s">
-        <v>89</v>
-      </c>
-      <c r="K16" s="27">
-        <v>2030</v>
-      </c>
-      <c r="L16">
-        <v>2018</v>
-      </c>
-      <c r="M16" t="s">
-        <v>109</v>
-      </c>
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16" s="27"/>
+      <c r="L16"/>
+      <c r="M16"/>
       <c r="N16"/>
-      <c r="O16">
-        <v>94.6</v>
-      </c>
-      <c r="P16" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>90</v>
-      </c>
-      <c r="R16" t="s">
-        <v>109</v>
-      </c>
-      <c r="S16" t="s">
-        <v>61</v>
-      </c>
-      <c r="T16" t="s">
-        <v>109</v>
-      </c>
-      <c r="U16" t="s">
-        <v>107</v>
-      </c>
-      <c r="V16" t="e">
-        <f>SUMIFS([1]Data_BY!J$2:J$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
       <c r="W16"/>
       <c r="X16"/>
       <c r="Y16"/>
@@ -14364,71 +10849,28 @@
       <c r="AN16"/>
     </row>
     <row r="17" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" t="s">
-        <v>89</v>
-      </c>
-      <c r="K17" s="27">
-        <v>2032</v>
-      </c>
-      <c r="L17">
-        <v>2018</v>
-      </c>
-      <c r="M17" t="s">
-        <v>109</v>
-      </c>
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17" s="27"/>
+      <c r="L17"/>
+      <c r="M17"/>
       <c r="N17"/>
-      <c r="O17">
-        <v>94.6</v>
-      </c>
-      <c r="P17" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>90</v>
-      </c>
-      <c r="R17" t="s">
-        <v>109</v>
-      </c>
-      <c r="S17" t="s">
-        <v>61</v>
-      </c>
-      <c r="T17" t="s">
-        <v>109</v>
-      </c>
-      <c r="U17" t="s">
-        <v>107</v>
-      </c>
-      <c r="V17" t="e">
-        <f>SUMIFS([1]Data_BY!K$2:K$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
       <c r="W17"/>
       <c r="X17"/>
       <c r="Y17"/>
@@ -14449,71 +10891,28 @@
       <c r="AN17"/>
     </row>
     <row r="18" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" t="s">
-        <v>115</v>
-      </c>
-      <c r="J18" t="s">
-        <v>89</v>
-      </c>
-      <c r="K18" s="27">
-        <v>2034</v>
-      </c>
-      <c r="L18">
-        <v>2018</v>
-      </c>
-      <c r="M18" t="s">
-        <v>109</v>
-      </c>
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18" s="27"/>
+      <c r="L18"/>
+      <c r="M18"/>
       <c r="N18"/>
-      <c r="O18">
-        <v>94.6</v>
-      </c>
-      <c r="P18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>90</v>
-      </c>
-      <c r="R18" t="s">
-        <v>109</v>
-      </c>
-      <c r="S18" t="s">
-        <v>61</v>
-      </c>
-      <c r="T18" t="s">
-        <v>109</v>
-      </c>
-      <c r="U18" t="s">
-        <v>107</v>
-      </c>
-      <c r="V18" t="e">
-        <f>SUMIFS([1]Data_BY!L$2:L$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
       <c r="W18"/>
       <c r="X18"/>
       <c r="Y18"/>
@@ -14534,71 +10933,28 @@
       <c r="AN18"/>
     </row>
     <row r="19" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" t="s">
-        <v>89</v>
-      </c>
-      <c r="K19" s="27">
-        <v>2036</v>
-      </c>
-      <c r="L19">
-        <v>2018</v>
-      </c>
-      <c r="M19" t="s">
-        <v>109</v>
-      </c>
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19" s="27"/>
+      <c r="L19"/>
+      <c r="M19"/>
       <c r="N19"/>
-      <c r="O19">
-        <v>94.6</v>
-      </c>
-      <c r="P19" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>90</v>
-      </c>
-      <c r="R19" t="s">
-        <v>109</v>
-      </c>
-      <c r="S19" t="s">
-        <v>61</v>
-      </c>
-      <c r="T19" t="s">
-        <v>109</v>
-      </c>
-      <c r="U19" t="s">
-        <v>107</v>
-      </c>
-      <c r="V19" t="e">
-        <f>SUMIFS([1]Data_BY!M$2:M$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
       <c r="W19"/>
       <c r="X19"/>
       <c r="Y19"/>
@@ -14619,71 +10975,28 @@
       <c r="AN19"/>
     </row>
     <row r="20" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" t="s">
-        <v>114</v>
-      </c>
-      <c r="I20" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" s="27">
-        <v>2038</v>
-      </c>
-      <c r="L20">
-        <v>2018</v>
-      </c>
-      <c r="M20" t="s">
-        <v>109</v>
-      </c>
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20" s="27"/>
+      <c r="L20"/>
+      <c r="M20"/>
       <c r="N20"/>
-      <c r="O20">
-        <v>94.6</v>
-      </c>
-      <c r="P20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>90</v>
-      </c>
-      <c r="R20" t="s">
-        <v>109</v>
-      </c>
-      <c r="S20" t="s">
-        <v>61</v>
-      </c>
-      <c r="T20" t="s">
-        <v>109</v>
-      </c>
-      <c r="U20" t="s">
-        <v>107</v>
-      </c>
-      <c r="V20" t="e">
-        <f>SUMIFS([1]Data_BY!N$2:N$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
       <c r="W20"/>
       <c r="X20"/>
       <c r="Y20"/>
@@ -14704,71 +11017,28 @@
       <c r="AN20"/>
     </row>
     <row r="21" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
-        <v>114</v>
-      </c>
-      <c r="I21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" s="27">
-        <v>2040</v>
-      </c>
-      <c r="L21">
-        <v>2018</v>
-      </c>
-      <c r="M21" t="s">
-        <v>109</v>
-      </c>
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21" s="27"/>
+      <c r="L21"/>
+      <c r="M21"/>
       <c r="N21"/>
-      <c r="O21">
-        <v>94.6</v>
-      </c>
-      <c r="P21" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21" t="s">
-        <v>61</v>
-      </c>
-      <c r="T21" t="s">
-        <v>109</v>
-      </c>
-      <c r="U21" t="s">
-        <v>107</v>
-      </c>
-      <c r="V21" t="e">
-        <f>SUMIFS([1]Data_BY!O$2:O$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
       <c r="W21"/>
       <c r="X21"/>
       <c r="Y21"/>
@@ -14789,1003 +11059,52 @@
       <c r="AN21"/>
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" t="s">
-        <v>89</v>
-      </c>
-      <c r="K22" s="27">
-        <v>2042</v>
-      </c>
-      <c r="L22">
-        <v>2018</v>
-      </c>
-      <c r="M22" t="s">
-        <v>109</v>
-      </c>
-      <c r="O22">
-        <v>94.6</v>
-      </c>
-      <c r="P22" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>90</v>
-      </c>
-      <c r="R22" t="s">
-        <v>109</v>
-      </c>
-      <c r="S22" t="s">
-        <v>61</v>
-      </c>
-      <c r="T22" t="s">
-        <v>109</v>
-      </c>
-      <c r="U22" t="s">
-        <v>107</v>
-      </c>
-      <c r="V22" t="e">
-        <f>SUMIFS([1]Data_BY!P$2:P$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K22" s="27"/>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="27">
-        <v>2044</v>
-      </c>
-      <c r="L23">
-        <v>2018</v>
-      </c>
-      <c r="M23" t="s">
-        <v>109</v>
-      </c>
-      <c r="O23">
-        <v>94.6</v>
-      </c>
-      <c r="P23" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>90</v>
-      </c>
-      <c r="R23" t="s">
-        <v>109</v>
-      </c>
-      <c r="S23" t="s">
-        <v>61</v>
-      </c>
-      <c r="T23" t="s">
-        <v>109</v>
-      </c>
-      <c r="U23" t="s">
-        <v>107</v>
-      </c>
-      <c r="V23" t="e">
-        <f>SUMIFS([1]Data_BY!Q$2:Q$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K23" s="27"/>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" t="s">
-        <v>115</v>
-      </c>
-      <c r="J24" t="s">
-        <v>89</v>
-      </c>
-      <c r="K24" s="27">
-        <v>2046</v>
-      </c>
-      <c r="L24">
-        <v>2018</v>
-      </c>
-      <c r="M24" t="s">
-        <v>109</v>
-      </c>
-      <c r="O24">
-        <v>94.6</v>
-      </c>
-      <c r="P24" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>90</v>
-      </c>
-      <c r="R24" t="s">
-        <v>109</v>
-      </c>
-      <c r="S24" t="s">
-        <v>61</v>
-      </c>
-      <c r="T24" t="s">
-        <v>109</v>
-      </c>
-      <c r="U24" t="s">
-        <v>107</v>
-      </c>
-      <c r="V24" t="e">
-        <f>SUMIFS([1]Data_BY!R$2:R$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K24" s="27"/>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" t="s">
-        <v>114</v>
-      </c>
-      <c r="I25" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
-      <c r="K25" s="27">
-        <v>2048</v>
-      </c>
-      <c r="L25">
-        <v>2018</v>
-      </c>
-      <c r="M25" t="s">
-        <v>109</v>
-      </c>
-      <c r="O25">
-        <v>94.6</v>
-      </c>
-      <c r="P25" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>90</v>
-      </c>
-      <c r="R25" t="s">
-        <v>109</v>
-      </c>
-      <c r="S25" t="s">
-        <v>61</v>
-      </c>
-      <c r="T25" t="s">
-        <v>109</v>
-      </c>
-      <c r="U25" t="s">
-        <v>107</v>
-      </c>
-      <c r="V25" t="e">
-        <f>SUMIFS([1]Data_BY!S$2:S$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K25" s="27"/>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" t="s">
-        <v>114</v>
-      </c>
-      <c r="I26" t="s">
-        <v>115</v>
-      </c>
-      <c r="J26" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="27">
-        <v>2050</v>
-      </c>
-      <c r="L26">
-        <v>2018</v>
-      </c>
-      <c r="M26" t="s">
-        <v>109</v>
-      </c>
-      <c r="O26">
-        <v>94.6</v>
-      </c>
-      <c r="P26" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>90</v>
-      </c>
-      <c r="R26" t="s">
-        <v>109</v>
-      </c>
-      <c r="S26" t="s">
-        <v>61</v>
-      </c>
-      <c r="T26" t="s">
-        <v>109</v>
-      </c>
-      <c r="U26" t="s">
-        <v>107</v>
-      </c>
-      <c r="V26" t="e">
-        <f>SUMIFS([1]Data_BY!T$2:T$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K26" s="27"/>
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" t="s">
-        <v>114</v>
-      </c>
-      <c r="I27" t="s">
-        <v>115</v>
-      </c>
-      <c r="J27" t="s">
-        <v>89</v>
-      </c>
-      <c r="K27" s="27">
-        <v>2052</v>
-      </c>
-      <c r="L27">
-        <v>2018</v>
-      </c>
-      <c r="M27" t="s">
-        <v>109</v>
-      </c>
-      <c r="O27">
-        <v>94.6</v>
-      </c>
-      <c r="P27" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>90</v>
-      </c>
-      <c r="R27" t="s">
-        <v>109</v>
-      </c>
-      <c r="S27" t="s">
-        <v>61</v>
-      </c>
-      <c r="T27" t="s">
-        <v>109</v>
-      </c>
-      <c r="U27" t="s">
-        <v>107</v>
-      </c>
-      <c r="V27" t="e">
-        <f>SUMIFS([1]Data_BY!U$2:U$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K27" s="27"/>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" t="s">
-        <v>100</v>
-      </c>
-      <c r="H28" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" t="s">
-        <v>115</v>
-      </c>
-      <c r="J28" t="s">
-        <v>89</v>
-      </c>
-      <c r="K28" s="27">
-        <v>2054</v>
-      </c>
-      <c r="L28">
-        <v>2018</v>
-      </c>
-      <c r="M28" t="s">
-        <v>109</v>
-      </c>
-      <c r="O28">
-        <v>94.6</v>
-      </c>
-      <c r="P28" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>90</v>
-      </c>
-      <c r="R28" t="s">
-        <v>109</v>
-      </c>
-      <c r="S28" t="s">
-        <v>61</v>
-      </c>
-      <c r="T28" t="s">
-        <v>109</v>
-      </c>
-      <c r="U28" t="s">
-        <v>107</v>
-      </c>
-      <c r="V28" t="e">
-        <f>SUMIFS([1]Data_BY!V$2:V$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K28" s="27"/>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" t="s">
-        <v>114</v>
-      </c>
-      <c r="I29" t="s">
-        <v>115</v>
-      </c>
-      <c r="J29" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="27">
-        <v>2056</v>
-      </c>
-      <c r="L29">
-        <v>2018</v>
-      </c>
-      <c r="M29" t="s">
-        <v>109</v>
-      </c>
-      <c r="O29">
-        <v>94.6</v>
-      </c>
-      <c r="P29" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>90</v>
-      </c>
-      <c r="R29" t="s">
-        <v>109</v>
-      </c>
-      <c r="S29" t="s">
-        <v>61</v>
-      </c>
-      <c r="T29" t="s">
-        <v>109</v>
-      </c>
-      <c r="U29" t="s">
-        <v>107</v>
-      </c>
-      <c r="V29" t="e">
-        <f>SUMIFS([1]Data_BY!W$2:W$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K29" s="27"/>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" t="s">
-        <v>115</v>
-      </c>
-      <c r="J30" t="s">
-        <v>89</v>
-      </c>
-      <c r="K30" s="27">
-        <v>2058</v>
-      </c>
-      <c r="L30">
-        <v>2018</v>
-      </c>
-      <c r="M30" t="s">
-        <v>109</v>
-      </c>
-      <c r="O30">
-        <v>94.6</v>
-      </c>
-      <c r="P30" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>90</v>
-      </c>
-      <c r="R30" t="s">
-        <v>109</v>
-      </c>
-      <c r="S30" t="s">
-        <v>61</v>
-      </c>
-      <c r="T30" t="s">
-        <v>109</v>
-      </c>
-      <c r="U30" t="s">
-        <v>107</v>
-      </c>
-      <c r="V30" t="e">
-        <f>SUMIFS([1]Data_BY!X$2:X$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K30" s="27"/>
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" t="s">
-        <v>100</v>
-      </c>
-      <c r="H31" t="s">
-        <v>114</v>
-      </c>
-      <c r="I31" t="s">
-        <v>115</v>
-      </c>
-      <c r="J31" t="s">
-        <v>89</v>
-      </c>
-      <c r="K31" s="27">
-        <v>2060</v>
-      </c>
-      <c r="L31">
-        <v>2018</v>
-      </c>
-      <c r="M31" t="s">
-        <v>109</v>
-      </c>
-      <c r="O31">
-        <v>94.6</v>
-      </c>
-      <c r="P31" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>90</v>
-      </c>
-      <c r="R31" t="s">
-        <v>109</v>
-      </c>
-      <c r="S31" t="s">
-        <v>61</v>
-      </c>
-      <c r="T31" t="s">
-        <v>109</v>
-      </c>
-      <c r="U31" t="s">
-        <v>107</v>
-      </c>
-      <c r="V31" t="e">
-        <f>SUMIFS([1]Data_BY!Y$2:Y$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K31" s="27"/>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" t="s">
-        <v>114</v>
-      </c>
-      <c r="I32" t="s">
-        <v>115</v>
-      </c>
-      <c r="J32" t="s">
-        <v>89</v>
-      </c>
-      <c r="K32" s="27">
-        <v>2062</v>
-      </c>
-      <c r="L32">
-        <v>2018</v>
-      </c>
-      <c r="M32" t="s">
-        <v>109</v>
-      </c>
-      <c r="O32">
-        <v>94.6</v>
-      </c>
-      <c r="P32" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>90</v>
-      </c>
-      <c r="R32" t="s">
-        <v>109</v>
-      </c>
-      <c r="S32" t="s">
-        <v>61</v>
-      </c>
-      <c r="T32" t="s">
-        <v>109</v>
-      </c>
-      <c r="U32" t="s">
-        <v>107</v>
-      </c>
-      <c r="V32" t="e">
-        <f>SUMIFS([1]Data_BY!Z$2:Z$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" t="s">
-        <v>114</v>
-      </c>
-      <c r="I33" t="s">
-        <v>115</v>
-      </c>
-      <c r="J33" t="s">
-        <v>89</v>
-      </c>
-      <c r="K33" s="27">
-        <v>2064</v>
-      </c>
-      <c r="L33">
-        <v>2018</v>
-      </c>
-      <c r="M33" t="s">
-        <v>109</v>
-      </c>
-      <c r="O33">
-        <v>94.6</v>
-      </c>
-      <c r="P33" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>90</v>
-      </c>
-      <c r="R33" t="s">
-        <v>109</v>
-      </c>
-      <c r="S33" t="s">
-        <v>61</v>
-      </c>
-      <c r="T33" t="s">
-        <v>109</v>
-      </c>
-      <c r="U33" t="s">
-        <v>107</v>
-      </c>
-      <c r="V33" t="e">
-        <f>SUMIFS([1]Data_BY!AA$2:AA$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" t="s">
-        <v>114</v>
-      </c>
-      <c r="I34" t="s">
-        <v>115</v>
-      </c>
-      <c r="J34" t="s">
-        <v>89</v>
-      </c>
-      <c r="K34" s="27">
-        <v>2066</v>
-      </c>
-      <c r="L34">
-        <v>2018</v>
-      </c>
-      <c r="M34" t="s">
-        <v>109</v>
-      </c>
-      <c r="O34">
-        <v>94.6</v>
-      </c>
-      <c r="P34" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>90</v>
-      </c>
-      <c r="R34" t="s">
-        <v>109</v>
-      </c>
-      <c r="S34" t="s">
-        <v>61</v>
-      </c>
-      <c r="T34" t="s">
-        <v>109</v>
-      </c>
-      <c r="U34" t="s">
-        <v>107</v>
-      </c>
-      <c r="V34" t="e">
-        <f>SUMIFS([1]Data_BY!AB$2:AB$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" t="s">
-        <v>115</v>
-      </c>
-      <c r="J35" t="s">
-        <v>89</v>
-      </c>
-      <c r="K35" s="27">
-        <v>2068</v>
-      </c>
-      <c r="L35">
-        <v>2018</v>
-      </c>
-      <c r="M35" t="s">
-        <v>109</v>
-      </c>
-      <c r="O35">
-        <v>94.6</v>
-      </c>
-      <c r="P35" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>90</v>
-      </c>
-      <c r="R35" t="s">
-        <v>109</v>
-      </c>
-      <c r="S35" t="s">
-        <v>61</v>
-      </c>
-      <c r="T35" t="s">
-        <v>109</v>
-      </c>
-      <c r="U35" t="s">
-        <v>107</v>
-      </c>
-      <c r="V35" t="e">
-        <f>SUMIFS([1]Data_BY!AC$2:AC$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" t="s">
-        <v>114</v>
-      </c>
-      <c r="I36" t="s">
-        <v>115</v>
-      </c>
-      <c r="J36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K36" s="27">
-        <v>2070</v>
-      </c>
-      <c r="L36">
-        <v>2018</v>
-      </c>
-      <c r="M36" t="s">
-        <v>109</v>
-      </c>
-      <c r="O36">
-        <v>94.6</v>
-      </c>
-      <c r="P36" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>90</v>
-      </c>
-      <c r="R36" t="s">
-        <v>109</v>
-      </c>
-      <c r="S36" t="s">
-        <v>61</v>
-      </c>
-      <c r="T36" t="s">
-        <v>109</v>
-      </c>
-      <c r="U36" t="s">
-        <v>107</v>
-      </c>
-      <c r="V36" t="e">
-        <f>SUMIFS([1]Data_BY!AD$2:AD$51,[1]Data_BY!$B$2:$B$51,[1]Import!$K7)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K32" s="27"/>
+    </row>
+    <row r="33" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="27"/>
+    </row>
+    <row r="34" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="27"/>
+    </row>
+    <row r="35" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="27"/>
+    </row>
+    <row r="36" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -15794,6 +11113,12 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15843,55 +11168,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -15996,9 +11321,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -16083,37 +11408,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -16372,18 +11697,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -17029,12 +12354,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -17043,6 +12362,12 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17091,55 +12416,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -17244,9 +12569,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -17331,37 +12656,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -17620,18 +12945,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -18453,12 +13778,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -18467,6 +13786,12 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18515,55 +13840,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -18668,9 +13993,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -18755,37 +14080,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -19044,18 +14369,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -19766,6 +15091,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -19774,12 +15105,6 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19828,55 +15153,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -19981,9 +15306,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -20068,37 +15393,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -20357,18 +15682,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -21079,6 +16404,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -21087,12 +16418,6 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21141,55 +16466,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -21294,9 +16619,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -21381,37 +16706,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -21670,18 +16995,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -22444,6 +17769,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -22452,12 +17783,6 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22506,55 +17831,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
       <c r="X1" s="29"/>
       <c r="Y1" s="29"/>
-      <c r="Z1" s="47" t="s">
+      <c r="Z1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="35" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="9"/>
     </row>
     <row r="2" spans="1:40" ht="32" x14ac:dyDescent="0.2">
@@ -22659,9 +17984,9 @@
       <c r="AI2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -22746,37 +18071,37 @@
         <v>42</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="39"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50" t="s">
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="39"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
-      <c r="Z4" s="51" t="s">
+      <c r="Z4" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="37" t="s">
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="AI4" s="38"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="18" t="s">
         <v>48</v>
       </c>
@@ -23035,18 +18360,18 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44" t="s">
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="44" t="s">
+      <c r="U9" s="52"/>
+      <c r="V9" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="45"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="30"/>
       <c r="Y9" s="30"/>
       <c r="Z9" s="8"/>
@@ -23761,6 +19086,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="Z1:AG1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AL2"/>
@@ -23769,12 +19100,6 @@
     <mergeCell ref="V9:W9"/>
     <mergeCell ref="Z4:AG4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="V4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23972,6 +19297,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="984c4d19-7ea2-4a6f-aeda-7b1561349114">
@@ -23979,15 +19313,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24009,6 +19334,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECD891E-2CC8-4942-ADB6-01326D874531}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1D803F4-625A-425E-8AAE-F12A11C703E0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="984c4d19-7ea2-4a6f-aeda-7b1561349114"/>
@@ -24022,12 +19355,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECD891E-2CC8-4942-ADB6-01326D874531}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>